--- a/DemonLordRoguelikeMod/Assets/Data/Excel/excel_mod_items_info_starlustsspine[Mod道具信息-StarLustsSpine].xlsx
+++ b/DemonLordRoguelikeMod/Assets/Data/Excel/excel_mod_items_info_starlustsspine[Mod道具信息-StarLustsSpine].xlsx
@@ -653,13 +653,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>ui_show_res:01_CG_SkeletonData&amp;ui_show_data:0.1378;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -673,7 +672,6 @@
           <t>星欲幻化药(StarLusts 01/CG/01_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>1</t>
@@ -701,13 +699,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>ui_show_res:01_Standard_SkeletonData&amp;ui_show_data:0.1654;0,0&amp;ui_show_skin:1</t>
@@ -721,7 +718,6 @@
           <t>星欲幻化药(StarLusts 01/Standard/01_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>1</t>
@@ -749,13 +745,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>ui_show_res:01_Standard_SkeletonData&amp;ui_show_data:0.1654;0,0&amp;ui_show_skin:2</t>
@@ -769,7 +764,6 @@
           <t>星欲幻化药(StarLusts 01/Standard/01_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>1</t>
@@ -797,13 +791,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>ui_show_res:01_Standard_SkeletonData&amp;ui_show_data:0.1654;0,0&amp;ui_show_skin:3</t>
@@ -817,7 +810,6 @@
           <t>星欲幻化药(StarLusts 01/Standard/01_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>1</t>
@@ -845,13 +837,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>ui_show_res:02_Standard_SkeletonData&amp;ui_show_data:0.3411;0,0&amp;ui_show_skin:1</t>
@@ -865,7 +856,6 @@
           <t>星欲幻化药(StarLusts 02/Standard/02_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>1</t>
@@ -893,13 +883,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>ui_show_res:02_Standard_SkeletonData&amp;ui_show_data:0.3411;0,0&amp;ui_show_skin:2</t>
@@ -913,7 +902,6 @@
           <t>星欲幻化药(StarLusts 02/Standard/02_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>1</t>
@@ -941,13 +929,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>ui_show_res:02_Standard_SkeletonData&amp;ui_show_data:0.3411;0,0&amp;ui_show_skin:3</t>
@@ -961,7 +948,6 @@
           <t>星欲幻化药(StarLusts 02/Standard/02_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>1</t>
@@ -989,13 +975,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>ui_show_res:03_CG_SkeletonData&amp;ui_show_data:0.123;0,0&amp;ui_show_idle_anim:InteractMode/P1_Idle</t>
@@ -1009,7 +994,6 @@
           <t>星欲幻化药(StarLusts 03/CG/03_CG_SkeletonData.asset default皮 idle:InteractMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>1</t>
@@ -1037,13 +1021,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>ui_show_res:03_Standard_SkeletonData&amp;ui_show_data:0.1496;0,0&amp;ui_show_skin:1</t>
@@ -1057,7 +1040,6 @@
           <t>星欲幻化药(StarLusts 03/Standard/03_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>1</t>
@@ -1085,13 +1067,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>ui_show_res:03_Standard_SkeletonData&amp;ui_show_data:0.1496;0,0&amp;ui_show_skin:2</t>
@@ -1105,7 +1086,6 @@
           <t>星欲幻化药(StarLusts 03/Standard/03_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>1</t>
@@ -1133,13 +1113,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>ui_show_res:03_Standard_SkeletonData&amp;ui_show_data:0.1496;0,0&amp;ui_show_skin:3</t>
@@ -1153,7 +1132,6 @@
           <t>星欲幻化药(StarLusts 03/Standard/03_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>1</t>
@@ -1181,13 +1159,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>ui_show_res:04_CG_SkeletonData&amp;ui_show_data:0.1887;0,0&amp;ui_show_idle_anim:InteractMode/P1_Idle</t>
@@ -1201,7 +1178,6 @@
           <t>星欲幻化药(StarLusts 04/CG/04_CG_SkeletonData.asset default皮 idle:InteractMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>1</t>
@@ -1229,13 +1205,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>ui_show_res:04_Standard_SkeletonData&amp;ui_show_data:0.1495;0,0&amp;ui_show_skin:1</t>
@@ -1249,7 +1224,6 @@
           <t>星欲幻化药(StarLusts 04/Standard/04_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>1</t>
@@ -1277,13 +1251,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>ui_show_res:04_Standard_SkeletonData&amp;ui_show_data:0.1495;0,0&amp;ui_show_skin:2</t>
@@ -1297,7 +1270,6 @@
           <t>星欲幻化药(StarLusts 04/Standard/04_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>1</t>
@@ -1325,13 +1297,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>ui_show_res:04_Standard_SkeletonData&amp;ui_show_data:0.1495;0,0&amp;ui_show_skin:3</t>
@@ -1345,7 +1316,6 @@
           <t>星欲幻化药(StarLusts 04/Standard/04_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>1</t>
@@ -1373,13 +1343,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>ui_show_res:05_Standard_SkeletonData&amp;ui_show_data:0.1804;0,0&amp;ui_show_skin:1</t>
@@ -1393,7 +1362,6 @@
           <t>星欲幻化药(StarLusts 05/Standard/05_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>1</t>
@@ -1421,13 +1389,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>ui_show_res:05_Standard_SkeletonData&amp;ui_show_data:0.1804;0,0&amp;ui_show_skin:2</t>
@@ -1441,7 +1408,6 @@
           <t>星欲幻化药(StarLusts 05/Standard/05_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>1</t>
@@ -1469,13 +1435,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>ui_show_res:05_Standard_SkeletonData&amp;ui_show_data:0.1804;0,0&amp;ui_show_skin:3</t>
@@ -1489,7 +1454,6 @@
           <t>星欲幻化药(StarLusts 05/Standard/05_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>1</t>
@@ -1517,13 +1481,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>ui_show_res:06_CG_SkeletonData&amp;ui_show_data:0.1612;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle 1</t>
@@ -1537,7 +1500,6 @@
           <t>星欲幻化药(StarLusts 06/CG/06_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle 1)</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>1</t>
@@ -1565,13 +1527,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>ui_show_res:06_Standard_SkeletonData&amp;ui_show_data:0.154;0,0&amp;ui_show_skin:1</t>
@@ -1585,7 +1546,6 @@
           <t>星欲幻化药(StarLusts 06/Standard/06_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>1</t>
@@ -1613,13 +1573,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>ui_show_res:06_Standard_SkeletonData&amp;ui_show_data:0.154;0,0&amp;ui_show_skin:2</t>
@@ -1633,7 +1592,6 @@
           <t>星欲幻化药(StarLusts 06/Standard/06_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>1</t>
@@ -1661,13 +1619,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>ui_show_res:06_Standard_SkeletonData&amp;ui_show_data:0.154;0,0&amp;ui_show_skin:3</t>
@@ -1681,7 +1638,6 @@
           <t>星欲幻化药(StarLusts 06/Standard/06_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>1</t>
@@ -1709,13 +1665,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>ui_show_res:07_CG_SkeletonData&amp;ui_show_data:0.1265;0,0&amp;ui_show_idle_anim:InteractMode/P1_Idle</t>
@@ -1729,7 +1684,6 @@
           <t>星欲幻化药(StarLusts 07/CG/07_CG_SkeletonData.asset default皮 idle:InteractMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>1</t>
@@ -1757,13 +1711,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>ui_show_res:07_Standard_SkeletonData&amp;ui_show_data:0.1797;0,0&amp;ui_show_skin:1</t>
@@ -1777,7 +1730,6 @@
           <t>星欲幻化药(StarLusts 07/Standard/07_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>1</t>
@@ -1805,13 +1757,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>ui_show_res:07_Standard_SkeletonData&amp;ui_show_data:0.1797;0,0&amp;ui_show_skin:2</t>
@@ -1825,7 +1776,6 @@
           <t>星欲幻化药(StarLusts 07/Standard/07_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>1</t>
@@ -1853,13 +1803,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>ui_show_res:07_Standard_SkeletonData&amp;ui_show_data:0.1797;0,0&amp;ui_show_skin:3</t>
@@ -1873,7 +1822,6 @@
           <t>星欲幻化药(StarLusts 07/Standard/07_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>1</t>
@@ -1901,13 +1849,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>ui_show_res:08_CG_SkeletonData&amp;ui_show_data:0.1171;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -1921,7 +1868,6 @@
           <t>星欲幻化药(StarLusts 08/CG/08_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>1</t>
@@ -1949,13 +1895,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>ui_show_res:08_Standard_SkeletonData&amp;ui_show_data:0.1278;0,0&amp;ui_show_skin:1</t>
@@ -1969,7 +1914,6 @@
           <t>星欲幻化药(StarLusts 08/Standard/08_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>1</t>
@@ -1997,13 +1941,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>ui_show_res:08_Standard_SkeletonData&amp;ui_show_data:0.1278;0,0&amp;ui_show_skin:2</t>
@@ -2017,7 +1960,6 @@
           <t>星欲幻化药(StarLusts 08/Standard/08_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>1</t>
@@ -2045,13 +1987,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>ui_show_res:08_Standard_SkeletonData&amp;ui_show_data:0.1278;0,0&amp;ui_show_skin:3</t>
@@ -2065,7 +2006,6 @@
           <t>星欲幻化药(StarLusts 08/Standard/08_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>1</t>
@@ -2093,13 +2033,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>ui_show_res:09_Standard_SkeletonData&amp;ui_show_data:0.169;0,0&amp;ui_show_skin:1</t>
@@ -2113,7 +2052,6 @@
           <t>星欲幻化药(StarLusts 09/Standard/09_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>1</t>
@@ -2141,13 +2079,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>ui_show_res:09_Standard_SkeletonData&amp;ui_show_data:0.169;0,0&amp;ui_show_skin:2</t>
@@ -2161,7 +2098,6 @@
           <t>星欲幻化药(StarLusts 09/Standard/09_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>1</t>
@@ -2189,13 +2125,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>ui_show_res:09_Standard_SkeletonData&amp;ui_show_data:0.169;0,0&amp;ui_show_skin:3</t>
@@ -2209,7 +2144,6 @@
           <t>星欲幻化药(StarLusts 09/Standard/09_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>1</t>
@@ -2237,13 +2171,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>ui_show_res:10_CG_SkeletonData&amp;ui_show_data:0.1421;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -2257,7 +2190,6 @@
           <t>星欲幻化药(StarLusts 10/CG/10_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>1</t>
@@ -2285,13 +2217,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>ui_show_res:10_Standard_SkeletonData&amp;ui_show_data:0.1664;0,0&amp;ui_show_skin:1</t>
@@ -2305,7 +2236,6 @@
           <t>星欲幻化药(StarLusts 10/Standard/10_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>1</t>
@@ -2333,13 +2263,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>ui_show_res:10_Standard_SkeletonData&amp;ui_show_data:0.1664;0,0&amp;ui_show_skin:2</t>
@@ -2353,7 +2282,6 @@
           <t>星欲幻化药(StarLusts 10/Standard/10_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>1</t>
@@ -2381,13 +2309,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>ui_show_res:10_Standard_SkeletonData&amp;ui_show_data:0.1664;0,0&amp;ui_show_skin:3</t>
@@ -2401,7 +2328,6 @@
           <t>星欲幻化药(StarLusts 10/Standard/10_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>1</t>
@@ -2429,13 +2355,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>ui_show_res:11_CG_SkeletonData&amp;ui_show_data:0.1288;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -2449,7 +2374,6 @@
           <t>星欲幻化药(StarLusts 11/CG/11_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>1</t>
@@ -2477,13 +2401,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>ui_show_res:11_Standard_SkeletonData&amp;ui_show_data:0.1664;0,0&amp;ui_show_skin:1</t>
@@ -2497,7 +2420,6 @@
           <t>星欲幻化药(StarLusts 11/Standard/11_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>1</t>
@@ -2525,13 +2447,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>ui_show_res:11_Standard_SkeletonData&amp;ui_show_data:0.1664;0,0&amp;ui_show_skin:2</t>
@@ -2545,7 +2466,6 @@
           <t>星欲幻化药(StarLusts 11/Standard/11_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>1</t>
@@ -2573,13 +2493,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>ui_show_res:11_Standard_SkeletonData&amp;ui_show_data:0.1664;0,0&amp;ui_show_skin:3</t>
@@ -2593,7 +2512,6 @@
           <t>星欲幻化药(StarLusts 11/Standard/11_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>1</t>
@@ -2621,13 +2539,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>ui_show_res:12_CG_SkeletonData&amp;ui_show_data:0.1402;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -2641,7 +2558,6 @@
           <t>星欲幻化药(StarLusts 12/CG/12_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>1</t>
@@ -2669,13 +2585,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>ui_show_res:12_Standard_SkeletonData&amp;ui_show_data:0.1511;0,0&amp;ui_show_skin:1</t>
@@ -2689,7 +2604,6 @@
           <t>星欲幻化药(StarLusts 12/Standard/12_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>1</t>
@@ -2717,13 +2631,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>ui_show_res:12_Standard_SkeletonData&amp;ui_show_data:0.1511;0,0&amp;ui_show_skin:2</t>
@@ -2737,7 +2650,6 @@
           <t>星欲幻化药(StarLusts 12/Standard/12_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>1</t>
@@ -2765,13 +2677,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>ui_show_res:12_Standard_SkeletonData&amp;ui_show_data:0.1511;0,0&amp;ui_show_skin:3</t>
@@ -2785,7 +2696,6 @@
           <t>星欲幻化药(StarLusts 12/Standard/12_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>1</t>
@@ -2813,13 +2723,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>ui_show_res:13_CG_SkeletonData&amp;ui_show_data:0.1492;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -2833,7 +2742,6 @@
           <t>星欲幻化药(StarLusts 13/CG/13_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>1</t>
@@ -2861,13 +2769,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>ui_show_res:13_Standard_SkeletonData&amp;ui_show_data:0.149;0,0&amp;ui_show_skin:1</t>
@@ -2881,7 +2788,6 @@
           <t>星欲幻化药(StarLusts 13/Standard/13_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>1</t>
@@ -2909,13 +2815,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>ui_show_res:13_Standard_SkeletonData&amp;ui_show_data:0.149;0,0&amp;ui_show_skin:2</t>
@@ -2929,7 +2834,6 @@
           <t>星欲幻化药(StarLusts 13/Standard/13_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>1</t>
@@ -2957,13 +2861,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>ui_show_res:13_Standard_SkeletonData&amp;ui_show_data:0.149;0,0&amp;ui_show_skin:3</t>
@@ -2977,7 +2880,6 @@
           <t>星欲幻化药(StarLusts 13/Standard/13_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>1</t>
@@ -3005,13 +2907,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>ui_show_res:14_Standard_SkeletonData&amp;ui_show_data:0.1401;0,0&amp;ui_show_skin:1</t>
@@ -3025,7 +2926,6 @@
           <t>星欲幻化药(StarLusts 14/Standard/14_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>1</t>
@@ -3053,13 +2953,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>ui_show_res:14_Standard_SkeletonData&amp;ui_show_data:0.1401;0,0&amp;ui_show_skin:2</t>
@@ -3073,7 +2972,6 @@
           <t>星欲幻化药(StarLusts 14/Standard/14_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>1</t>
@@ -3101,13 +2999,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>ui_show_res:14_Standard_SkeletonData&amp;ui_show_data:0.1401;0,0&amp;ui_show_skin:3</t>
@@ -3121,7 +3018,6 @@
           <t>星欲幻化药(StarLusts 14/Standard/14_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>1</t>
@@ -3149,13 +3045,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>ui_show_res:15_CG_SkeletonData&amp;ui_show_data:0.1151;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -3169,7 +3064,6 @@
           <t>星欲幻化药(StarLusts 15/CG/15_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>1</t>
@@ -3197,13 +3091,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>ui_show_res:15_Standard_SkeletonData&amp;ui_show_data:0.0984;0,0&amp;ui_show_skin:1</t>
@@ -3217,7 +3110,6 @@
           <t>星欲幻化药(StarLusts 15/Standard/15_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
           <t>1</t>
@@ -3245,13 +3137,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>ui_show_res:15_Standard_SkeletonData&amp;ui_show_data:0.0984;0,0&amp;ui_show_skin:2</t>
@@ -3265,7 +3156,6 @@
           <t>星欲幻化药(StarLusts 15/Standard/15_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>1</t>
@@ -3293,13 +3183,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>ui_show_res:15_Standard_SkeletonData&amp;ui_show_data:0.0984;0,0&amp;ui_show_skin:3</t>
@@ -3313,7 +3202,6 @@
           <t>星欲幻化药(StarLusts 15/Standard/15_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>1</t>
@@ -3341,13 +3229,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>ui_show_res:16_Standard_SkeletonData&amp;ui_show_data:0.1088;0,0&amp;ui_show_skin:1</t>
@@ -3361,7 +3248,6 @@
           <t>星欲幻化药(StarLusts 16/Standard/16_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>1</t>
@@ -3389,13 +3275,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>ui_show_res:16_Standard_SkeletonData&amp;ui_show_data:0.1088;0,0&amp;ui_show_skin:2</t>
@@ -3409,7 +3294,6 @@
           <t>星欲幻化药(StarLusts 16/Standard/16_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>1</t>
@@ -3437,13 +3321,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>ui_show_res:16_Standard_SkeletonData&amp;ui_show_data:0.1088;0,0&amp;ui_show_skin:3</t>
@@ -3457,7 +3340,6 @@
           <t>星欲幻化药(StarLusts 16/Standard/16_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>1</t>
@@ -3485,13 +3367,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>ui_show_res:17_Standard_SkeletonData&amp;ui_show_data:0.1313;0,0&amp;ui_show_skin:1</t>
@@ -3505,7 +3386,6 @@
           <t>星欲幻化药(StarLusts 17/Standard/17_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>1</t>
@@ -3533,13 +3413,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>ui_show_res:17_Standard_SkeletonData&amp;ui_show_data:0.1313;0,0&amp;ui_show_skin:2</t>
@@ -3553,7 +3432,6 @@
           <t>星欲幻化药(StarLusts 17/Standard/17_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>1</t>
@@ -3581,13 +3459,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>ui_show_res:17_Standard_SkeletonData&amp;ui_show_data:0.1313;0,0&amp;ui_show_skin:3</t>
@@ -3601,7 +3478,6 @@
           <t>星欲幻化药(StarLusts 17/Standard/17_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>1</t>
@@ -3629,13 +3505,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>ui_show_res:19_HCG_SkeletonData&amp;ui_show_data:0.1289;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -3649,7 +3524,6 @@
           <t>星欲幻化药(StarLusts 19/HCG/19_HCG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>1</t>
@@ -3677,13 +3551,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>ui_show_res:19_Standard_SkeletonData&amp;ui_show_data:0.1334;0,0&amp;ui_show_skin:1</t>
@@ -3697,7 +3570,6 @@
           <t>星欲幻化药(StarLusts 19/Standard/19_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>1</t>
@@ -3725,13 +3597,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>ui_show_res:19_Standard_SkeletonData&amp;ui_show_data:0.1334;0,0&amp;ui_show_skin:2</t>
@@ -3745,7 +3616,6 @@
           <t>星欲幻化药(StarLusts 19/Standard/19_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>1</t>
@@ -3773,13 +3643,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>ui_show_res:19_Standard_SkeletonData&amp;ui_show_data:0.1334;0,0&amp;ui_show_skin:3</t>
@@ -3793,7 +3662,6 @@
           <t>星欲幻化药(StarLusts 19/Standard/19_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>1</t>
@@ -3821,13 +3689,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>ui_show_res:20_Standard_SkeletonData&amp;ui_show_data:0.1536;0,0&amp;ui_show_skin:1</t>
@@ -3841,7 +3708,6 @@
           <t>星欲幻化药(StarLusts 20/Standard/20_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
           <t>1</t>
@@ -3869,13 +3735,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>ui_show_res:20_Standard_SkeletonData&amp;ui_show_data:0.1536;0,0&amp;ui_show_skin:2</t>
@@ -3889,7 +3754,6 @@
           <t>星欲幻化药(StarLusts 20/Standard/20_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>1</t>
@@ -3917,13 +3781,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>ui_show_res:20_Standard_SkeletonData&amp;ui_show_data:0.1536;0,0&amp;ui_show_skin:3</t>
@@ -3937,7 +3800,6 @@
           <t>星欲幻化药(StarLusts 20/Standard/20_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>1</t>
@@ -3965,13 +3827,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>ui_show_res:21_Standard_SkeletonData&amp;ui_show_data:0.1054;0,0&amp;ui_show_skin:1</t>
@@ -3985,7 +3846,6 @@
           <t>星欲幻化药(StarLusts 21/Standard/21_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>1</t>
@@ -4013,13 +3873,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>ui_show_res:21_Standard_SkeletonData&amp;ui_show_data:0.1054;0,0&amp;ui_show_skin:2</t>
@@ -4033,7 +3892,6 @@
           <t>星欲幻化药(StarLusts 21/Standard/21_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>1</t>
@@ -4061,13 +3919,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>ui_show_res:21_Standard_SkeletonData&amp;ui_show_data:0.1054;0,0&amp;ui_show_skin:3</t>
@@ -4081,7 +3938,6 @@
           <t>星欲幻化药(StarLusts 21/Standard/21_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>1</t>
@@ -4109,13 +3965,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>ui_show_res:22_CG_SkeletonData&amp;ui_show_data:0.0987;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -4129,7 +3984,6 @@
           <t>星欲幻化药(StarLusts 22/CG/22_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>1</t>
@@ -4157,13 +4011,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>ui_show_res:22_Standard_SkeletonData&amp;ui_show_data:0.1209;0,0&amp;ui_show_skin:1</t>
@@ -4177,7 +4030,6 @@
           <t>星欲幻化药(StarLusts 22/Standard/22_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
           <t>1</t>
@@ -4205,13 +4057,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>ui_show_res:22_Standard_SkeletonData&amp;ui_show_data:0.1209;0,0&amp;ui_show_skin:2</t>
@@ -4225,7 +4076,6 @@
           <t>星欲幻化药(StarLusts 22/Standard/22_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
           <t>1</t>
@@ -4253,13 +4103,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>ui_show_res:22_Standard_SkeletonData&amp;ui_show_data:0.1209;0,0&amp;ui_show_skin:3</t>
@@ -4273,7 +4122,6 @@
           <t>星欲幻化药(StarLusts 22/Standard/22_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>1</t>
@@ -4301,13 +4149,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>ui_show_res:23_Standard_SkeletonData&amp;ui_show_data:0.1295;0,0&amp;ui_show_skin:1</t>
@@ -4321,7 +4168,6 @@
           <t>星欲幻化药(StarLusts 23/Standard/23_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>1</t>
@@ -4349,13 +4195,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>ui_show_res:23_Standard_SkeletonData&amp;ui_show_data:0.1295;0,0&amp;ui_show_skin:2</t>
@@ -4369,7 +4214,6 @@
           <t>星欲幻化药(StarLusts 23/Standard/23_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>1</t>
@@ -4397,13 +4241,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>ui_show_res:23_Standard_SkeletonData&amp;ui_show_data:0.1295;0,0&amp;ui_show_skin:3</t>
@@ -4417,7 +4260,6 @@
           <t>星欲幻化药(StarLusts 23/Standard/23_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
           <t>1</t>
@@ -4445,13 +4287,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>ui_show_res:24_CG_SkeletonData&amp;ui_show_data:0.1003;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -4465,7 +4306,6 @@
           <t>星欲幻化药(StarLusts 24/CG/24_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
           <t>1</t>
@@ -4493,13 +4333,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H84" t="n">
         <v>0</v>
       </c>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>ui_show_res:24_Standard_SkeletonData&amp;ui_show_data:0.1537;0,0&amp;ui_show_skin:1</t>
@@ -4513,7 +4352,6 @@
           <t>星欲幻化药(StarLusts 24/Standard/24_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
           <t>1</t>
@@ -4541,13 +4379,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H85" t="n">
         <v>0</v>
       </c>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>ui_show_res:24_Standard_SkeletonData&amp;ui_show_data:0.1537;0,0&amp;ui_show_skin:2</t>
@@ -4561,7 +4398,6 @@
           <t>星欲幻化药(StarLusts 24/Standard/24_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
           <t>1</t>
@@ -4589,13 +4425,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>ui_show_res:24_Standard_SkeletonData&amp;ui_show_data:0.1537;0,0&amp;ui_show_skin:3</t>
@@ -4609,7 +4444,6 @@
           <t>星欲幻化药(StarLusts 24/Standard/24_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
           <t>1</t>
@@ -4637,13 +4471,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>ui_show_res:25_Standard_SkeletonData&amp;ui_show_data:0.1311;0,0&amp;ui_show_skin:1</t>
@@ -4657,7 +4490,6 @@
           <t>星欲幻化药(StarLusts 25/Standard/25_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
           <t>1</t>
@@ -4685,13 +4517,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H88" t="n">
         <v>0</v>
       </c>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>ui_show_res:25_Standard_SkeletonData&amp;ui_show_data:0.1311;0,0&amp;ui_show_skin:2</t>
@@ -4705,7 +4536,6 @@
           <t>星欲幻化药(StarLusts 25/Standard/25_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
           <t>1</t>
@@ -4733,13 +4563,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H89" t="n">
         <v>0</v>
       </c>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>ui_show_res:25_Standard_SkeletonData&amp;ui_show_data:0.1311;0,0&amp;ui_show_skin:3</t>
@@ -4753,7 +4582,6 @@
           <t>星欲幻化药(StarLusts 25/Standard/25_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
           <t>1</t>
@@ -4781,13 +4609,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>ui_show_res:26_CG_SkeletonData&amp;ui_show_data:0.1286;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -4801,7 +4628,6 @@
           <t>星欲幻化药(StarLusts 26/CG/26_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>1</t>
@@ -4829,13 +4655,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>ui_show_res:26_Standard_SkeletonData&amp;ui_show_data:0.139;0,0&amp;ui_show_skin:1</t>
@@ -4849,7 +4674,6 @@
           <t>星欲幻化药(StarLusts 26/Standard/26_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>1</t>
@@ -4877,13 +4701,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>ui_show_res:26_Standard_SkeletonData&amp;ui_show_data:0.139;0,0&amp;ui_show_skin:2</t>
@@ -4897,7 +4720,6 @@
           <t>星欲幻化药(StarLusts 26/Standard/26_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
           <t>1</t>
@@ -4925,13 +4747,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>ui_show_res:26_Standard_SkeletonData&amp;ui_show_data:0.139;0,0&amp;ui_show_skin:3</t>
@@ -4945,7 +4766,6 @@
           <t>星欲幻化药(StarLusts 26/Standard/26_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
           <t>1</t>
@@ -4973,13 +4793,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H94" t="n">
         <v>0</v>
       </c>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>ui_show_res:27_CG_SkeletonData&amp;ui_show_data:0.1289;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -4993,7 +4812,6 @@
           <t>星欲幻化药(StarLusts 27/CG/27_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
           <t>1</t>
@@ -5021,13 +4839,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H95" t="n">
         <v>0</v>
       </c>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>ui_show_res:27_Standard_SkeletonData&amp;ui_show_data:0.1736;0,0&amp;ui_show_skin:1</t>
@@ -5041,7 +4858,6 @@
           <t>星欲幻化药(StarLusts 27/Standard/27_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
           <t>1</t>
@@ -5069,13 +4885,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H96" t="n">
         <v>0</v>
       </c>
-      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>ui_show_res:27_Standard_SkeletonData&amp;ui_show_data:0.1736;0,0&amp;ui_show_skin:2</t>
@@ -5089,7 +4904,6 @@
           <t>星欲幻化药(StarLusts 27/Standard/27_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
           <t>1</t>
@@ -5117,13 +4931,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H97" t="n">
         <v>0</v>
       </c>
-      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>ui_show_res:27_Standard_SkeletonData&amp;ui_show_data:0.1736;0,0&amp;ui_show_skin:3</t>
@@ -5137,7 +4950,6 @@
           <t>星欲幻化药(StarLusts 27/Standard/27_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
           <t>1</t>
@@ -5165,13 +4977,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H98" t="n">
         <v>0</v>
       </c>
-      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>ui_show_res:28_CG_SkeletonData&amp;ui_show_data:0.1206;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -5185,7 +4996,6 @@
           <t>星欲幻化药(StarLusts 28/CG/28_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
           <t>1</t>
@@ -5213,13 +5023,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>ui_show_res:28_Standard_SkeletonData&amp;ui_show_data:0.1313;0,0&amp;ui_show_skin:1</t>
@@ -5233,7 +5042,6 @@
           <t>星欲幻化药(StarLusts 28/Standard/28_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
           <t>1</t>
@@ -5261,13 +5069,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>ui_show_res:28_Standard_SkeletonData&amp;ui_show_data:0.1313;0,0&amp;ui_show_skin:2</t>
@@ -5281,7 +5088,6 @@
           <t>星欲幻化药(StarLusts 28/Standard/28_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
           <t>1</t>
@@ -5309,13 +5115,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H101" t="n">
         <v>0</v>
       </c>
-      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>ui_show_res:28_Standard_SkeletonData&amp;ui_show_data:0.1313;0,0&amp;ui_show_skin:3</t>
@@ -5329,7 +5134,6 @@
           <t>星欲幻化药(StarLusts 28/Standard/28_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
           <t>1</t>
@@ -5357,13 +5161,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H102" t="n">
         <v>0</v>
       </c>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>ui_show_res:29_Standard_SkeletonData&amp;ui_show_data:0.1088;0,0&amp;ui_show_skin:1</t>
@@ -5377,7 +5180,6 @@
           <t>星欲幻化药(StarLusts 29/Standard/29_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
           <t>1</t>
@@ -5405,13 +5207,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H103" t="n">
         <v>0</v>
       </c>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>ui_show_res:29_Standard_SkeletonData&amp;ui_show_data:0.1088;0,0&amp;ui_show_skin:2</t>
@@ -5425,7 +5226,6 @@
           <t>星欲幻化药(StarLusts 29/Standard/29_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
           <t>1</t>
@@ -5453,13 +5253,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H104" t="n">
         <v>0</v>
       </c>
-      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>ui_show_res:29_Standard_SkeletonData&amp;ui_show_data:0.1088;0,0&amp;ui_show_skin:3</t>
@@ -5473,7 +5272,6 @@
           <t>星欲幻化药(StarLusts 29/Standard/29_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
           <t>1</t>
@@ -5501,13 +5299,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H105" t="n">
         <v>0</v>
       </c>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>ui_show_res:30_CG_SkeletonData&amp;ui_show_data:0.1212;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -5521,7 +5318,6 @@
           <t>星欲幻化药(StarLusts 30/CG/30_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
           <t>1</t>
@@ -5549,13 +5345,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H106" t="n">
         <v>0</v>
       </c>
-      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>ui_show_res:30_Standard_SkeletonData&amp;ui_show_data:0.1532;0,0&amp;ui_show_skin:1</t>
@@ -5569,7 +5364,6 @@
           <t>星欲幻化药(StarLusts 30/Standard/30_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
           <t>1</t>
@@ -5597,13 +5391,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H107" t="n">
         <v>0</v>
       </c>
-      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>ui_show_res:30_Standard_SkeletonData&amp;ui_show_data:0.1532;0,0&amp;ui_show_skin:2</t>
@@ -5617,7 +5410,6 @@
           <t>星欲幻化药(StarLusts 30/Standard/30_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
           <t>1</t>
@@ -5645,13 +5437,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H108" t="n">
         <v>0</v>
       </c>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>ui_show_res:30_Standard_SkeletonData&amp;ui_show_data:0.1532;0,0&amp;ui_show_skin:3</t>
@@ -5665,7 +5456,6 @@
           <t>星欲幻化药(StarLusts 30/Standard/30_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
           <t>1</t>
@@ -5693,13 +5483,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>ui_show_res:31_CG_SkeletonData&amp;ui_show_data:0.1111;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -5713,7 +5502,6 @@
           <t>星欲幻化药(StarLusts 31/CG/31_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
           <t>1</t>
@@ -5741,13 +5529,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H110" t="n">
         <v>0</v>
       </c>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>ui_show_res:31_Standard_SkeletonData&amp;ui_show_data:0.1367;0,0&amp;ui_show_skin:1</t>
@@ -5761,7 +5548,6 @@
           <t>星欲幻化药(StarLusts 31/Standard/31_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
           <t>1</t>
@@ -5789,13 +5575,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H111" t="n">
         <v>0</v>
       </c>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>ui_show_res:31_Standard_SkeletonData&amp;ui_show_data:0.1367;0,0&amp;ui_show_skin:2</t>
@@ -5809,7 +5594,6 @@
           <t>星欲幻化药(StarLusts 31/Standard/31_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
           <t>1</t>
@@ -5837,13 +5621,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H112" t="n">
         <v>0</v>
       </c>
-      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>ui_show_res:31_Standard_SkeletonData&amp;ui_show_data:0.1367;0,0&amp;ui_show_skin:3</t>
@@ -5857,7 +5640,6 @@
           <t>星欲幻化药(StarLusts 31/Standard/31_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr">
         <is>
           <t>1</t>
@@ -5885,13 +5667,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H113" t="n">
         <v>0</v>
       </c>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>ui_show_res:32_CG_SkeletonData&amp;ui_show_data:0.1107;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -5905,7 +5686,6 @@
           <t>星欲幻化药(StarLusts 32/CG/32_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
           <t>1</t>
@@ -5933,13 +5713,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H114" t="n">
         <v>0</v>
       </c>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>ui_show_res:32_Standard_SkeletonData&amp;ui_show_data:0.1546;0,0&amp;ui_show_skin:1</t>
@@ -5953,7 +5732,6 @@
           <t>星欲幻化药(StarLusts 32/Standard/32_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
           <t>1</t>
@@ -5981,13 +5759,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H115" t="n">
         <v>0</v>
       </c>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>ui_show_res:32_Standard_SkeletonData&amp;ui_show_data:0.1546;0,0&amp;ui_show_skin:2</t>
@@ -6001,7 +5778,6 @@
           <t>星欲幻化药(StarLusts 32/Standard/32_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
           <t>1</t>
@@ -6029,13 +5805,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H116" t="n">
         <v>0</v>
       </c>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>ui_show_res:32_Standard_SkeletonData&amp;ui_show_data:0.1546;0,0&amp;ui_show_skin:3</t>
@@ -6049,7 +5824,6 @@
           <t>星欲幻化药(StarLusts 32/Standard/32_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
           <t>1</t>
@@ -6077,13 +5851,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H117" t="n">
         <v>0</v>
       </c>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>ui_show_res:33_CG_SkeletonData&amp;ui_show_data:0.1258;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -6097,7 +5870,6 @@
           <t>星欲幻化药(StarLusts 33/CG/33_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
         <is>
           <t>1</t>
@@ -6125,13 +5897,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H118" t="n">
         <v>0</v>
       </c>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>ui_show_res:33_Standard_SkeletonData&amp;ui_show_data:0.1352;0,0&amp;ui_show_skin:1</t>
@@ -6145,7 +5916,6 @@
           <t>星欲幻化药(StarLusts 33/Standard/33_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
           <t>1</t>
@@ -6173,13 +5943,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H119" t="n">
         <v>0</v>
       </c>
-      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>ui_show_res:33_Standard_SkeletonData&amp;ui_show_data:0.1352;0,0&amp;ui_show_skin:2</t>
@@ -6193,7 +5962,6 @@
           <t>星欲幻化药(StarLusts 33/Standard/33_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
           <t>1</t>
@@ -6221,13 +5989,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H120" t="n">
         <v>0</v>
       </c>
-      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>ui_show_res:33_Standard_SkeletonData&amp;ui_show_data:0.1352;0,0&amp;ui_show_skin:3</t>
@@ -6241,7 +6008,6 @@
           <t>星欲幻化药(StarLusts 33/Standard/33_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr">
         <is>
           <t>1</t>
@@ -6269,13 +6035,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H121" t="n">
         <v>0</v>
       </c>
-      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>ui_show_res:34_CG_SkeletonData&amp;ui_show_data:0.103;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -6289,7 +6054,6 @@
           <t>星欲幻化药(StarLusts 34/CG/34_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr">
         <is>
           <t>1</t>
@@ -6317,13 +6081,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H122" t="n">
         <v>0</v>
       </c>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>ui_show_res:34_Standard_SkeletonData&amp;ui_show_data:0.1015;0,0&amp;ui_show_skin:1</t>
@@ -6337,7 +6100,6 @@
           <t>星欲幻化药(StarLusts 34/Standard/34_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr">
         <is>
           <t>1</t>
@@ -6365,13 +6127,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
-      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>ui_show_res:34_Standard_SkeletonData&amp;ui_show_data:0.1015;0,0&amp;ui_show_skin:2</t>
@@ -6385,7 +6146,6 @@
           <t>星欲幻化药(StarLusts 34/Standard/34_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr">
         <is>
           <t>1</t>
@@ -6413,13 +6173,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H124" t="n">
         <v>0</v>
       </c>
-      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>ui_show_res:34_Standard_SkeletonData&amp;ui_show_data:0.1015;0,0&amp;ui_show_skin:3</t>
@@ -6433,7 +6192,6 @@
           <t>星欲幻化药(StarLusts 34/Standard/34_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr">
         <is>
           <t>1</t>
@@ -6461,13 +6219,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H125" t="n">
         <v>0</v>
       </c>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>ui_show_res:104_CG_SkeletonData&amp;ui_show_data:0.1106;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -6481,7 +6238,6 @@
           <t>星欲幻化药(StarLusts 104/CG/104_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr">
         <is>
           <t>1</t>
@@ -6509,13 +6265,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>ui_show_res:104_Standard_SkeletonData&amp;ui_show_data:0.1231;0,0&amp;ui_show_skin:1</t>
@@ -6529,7 +6284,6 @@
           <t>星欲幻化药(StarLusts 104/Standard/104_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
           <t>1</t>
@@ -6557,13 +6311,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H127" t="n">
         <v>0</v>
       </c>
-      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>ui_show_res:104_Standard_SkeletonData&amp;ui_show_data:0.1231;0,0&amp;ui_show_skin:2</t>
@@ -6577,7 +6330,6 @@
           <t>星欲幻化药(StarLusts 104/Standard/104_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr">
         <is>
           <t>1</t>
@@ -6605,13 +6357,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H128" t="n">
         <v>0</v>
       </c>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>ui_show_res:104_Standard_SkeletonData&amp;ui_show_data:0.1231;0,0&amp;ui_show_skin:3</t>
@@ -6625,7 +6376,6 @@
           <t>星欲幻化药(StarLusts 104/Standard/104_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr">
         <is>
           <t>1</t>
@@ -6653,13 +6403,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
-      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>ui_show_res:108_CG_SkeletonData&amp;ui_show_data:0.1232;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -6673,7 +6422,6 @@
           <t>星欲幻化药(StarLusts 108/CG/108_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
           <t>1</t>
@@ -6701,13 +6449,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H130" t="n">
         <v>0</v>
       </c>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>ui_show_res:108_Standard_SkeletonData&amp;ui_show_data:0.1471;0,0&amp;ui_show_skin:1</t>
@@ -6721,7 +6468,6 @@
           <t>星欲幻化药(StarLusts 108/Standard/108_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr">
         <is>
           <t>1</t>
@@ -6749,13 +6495,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
-      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>ui_show_res:108_Standard_SkeletonData&amp;ui_show_data:0.1471;0,0&amp;ui_show_skin:2</t>
@@ -6769,7 +6514,6 @@
           <t>星欲幻化药(StarLusts 108/Standard/108_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr">
         <is>
           <t>1</t>
@@ -6797,13 +6541,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H132" t="n">
         <v>0</v>
       </c>
-      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>ui_show_res:108_Standard_SkeletonData&amp;ui_show_data:0.1471;0,0&amp;ui_show_skin:3</t>
@@ -6817,7 +6560,6 @@
           <t>星欲幻化药(StarLusts 108/Standard/108_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr">
         <is>
           <t>1</t>
@@ -6845,13 +6587,12 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H133" t="n">
         <v>0</v>
       </c>
-      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>ui_show_res:1001_Standard_SkeletonData&amp;ui_show_data:0.1499;0,0&amp;ui_show_skin:1</t>
@@ -6865,7 +6606,6 @@
           <t>星欲幻化药(StarLusts 1001/Standard/1001_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr">
         <is>
           <t>1</t>
@@ -6893,13 +6633,12 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H134" t="n">
         <v>0</v>
       </c>
-      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>ui_show_res:1001_Standard_SkeletonData&amp;ui_show_data:0.1499;0,0&amp;ui_show_skin:2</t>
@@ -6913,7 +6652,6 @@
           <t>星欲幻化药(StarLusts 1001/Standard/1001_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr">
         <is>
           <t>1</t>
@@ -6941,13 +6679,12 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H135" t="n">
         <v>0</v>
       </c>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>ui_show_res:1001_Standard_SkeletonData&amp;ui_show_data:0.1499;0,0&amp;ui_show_skin:3</t>
@@ -6961,7 +6698,6 @@
           <t>星欲幻化药(StarLusts 1001/Standard/1001_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr">
         <is>
           <t>1</t>
@@ -6989,13 +6725,12 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H136" t="n">
         <v>0</v>
       </c>
-      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>ui_show_res:1002_Standard_SkeletonData&amp;ui_show_data:0.1821;0,0&amp;ui_show_skin:1</t>
@@ -7009,7 +6744,6 @@
           <t>星欲幻化药(StarLusts 1002/Standard/1002_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr">
         <is>
           <t>1</t>
@@ -7037,13 +6771,12 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H137" t="n">
         <v>0</v>
       </c>
-      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>ui_show_res:1002_Standard_SkeletonData&amp;ui_show_data:0.1821;0,0&amp;ui_show_skin:2</t>
@@ -7057,7 +6790,6 @@
           <t>星欲幻化药(StarLusts 1002/Standard/1002_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr">
         <is>
           <t>1</t>
@@ -7085,13 +6817,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H138" t="n">
         <v>0</v>
       </c>
-      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>ui_show_res:1002_Standard_SkeletonData&amp;ui_show_data:0.1821;0,0&amp;ui_show_skin:3</t>
@@ -7105,7 +6836,6 @@
           <t>星欲幻化药(StarLusts 1002/Standard/1002_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr">
         <is>
           <t>1</t>
@@ -7133,13 +6863,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H139" t="n">
         <v>0</v>
       </c>
-      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>ui_show_res:1003_Standard_SkeletonData&amp;ui_show_data:0.1805;0,0&amp;ui_show_skin:1</t>
@@ -7153,7 +6882,6 @@
           <t>星欲幻化药(StarLusts 1003/Standard/1003_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr">
         <is>
           <t>1</t>
@@ -7181,13 +6909,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H140" t="n">
         <v>0</v>
       </c>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>ui_show_res:1003_Standard_SkeletonData&amp;ui_show_data:0.1805;0,0&amp;ui_show_skin:2</t>
@@ -7201,7 +6928,6 @@
           <t>星欲幻化药(StarLusts 1003/Standard/1003_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr">
         <is>
           <t>1</t>
@@ -7229,13 +6955,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H141" t="n">
         <v>0</v>
       </c>
-      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>ui_show_res:1003_Standard_SkeletonData&amp;ui_show_data:0.1805;0,0&amp;ui_show_skin:3</t>
@@ -7249,7 +6974,6 @@
           <t>星欲幻化药(StarLusts 1003/Standard/1003_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr">
         <is>
           <t>1</t>
@@ -7277,13 +7001,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H142" t="n">
         <v>0</v>
       </c>
-      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>ui_show_res:1004_Standard_SkeletonData&amp;ui_show_data:0.1133;0,0&amp;ui_show_skin:1</t>
@@ -7297,7 +7020,6 @@
           <t>星欲幻化药(StarLusts 1004/Standard/1004_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr">
         <is>
           <t>1</t>
@@ -7325,13 +7047,12 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H143" t="n">
         <v>0</v>
       </c>
-      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>ui_show_res:1004_Standard_SkeletonData&amp;ui_show_data:0.1133;0,0&amp;ui_show_skin:2</t>
@@ -7345,7 +7066,6 @@
           <t>星欲幻化药(StarLusts 1004/Standard/1004_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr">
         <is>
           <t>1</t>
@@ -7373,13 +7093,12 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H144" t="n">
         <v>0</v>
       </c>
-      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>ui_show_res:1004_Standard_SkeletonData&amp;ui_show_data:0.1133;0,0&amp;ui_show_skin:3</t>
@@ -7393,7 +7112,6 @@
           <t>星欲幻化药(StarLusts 1004/Standard/1004_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr">
         <is>
           <t>1</t>
@@ -7421,13 +7139,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H145" t="n">
         <v>0</v>
       </c>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>ui_show_res:1005_CG_SkeletonData&amp;ui_show_data:0.139;0,0&amp;ui_show_idle_anim:Interactive/P1_Idle</t>
@@ -7441,7 +7158,6 @@
           <t>星欲幻化药(StarLusts 1005/CG/1005_CG_SkeletonData.asset default皮 idle:Interactive/P1_Idle)</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr">
         <is>
           <t>1</t>
@@ -7469,13 +7185,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
-      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>ui_show_res:1005_Standard_SkeletonData&amp;ui_show_data:0.1312;0,0&amp;ui_show_skin:1</t>
@@ -7489,7 +7204,6 @@
           <t>星欲幻化药(StarLusts 1005/Standard/1005_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr">
         <is>
           <t>1</t>
@@ -7517,13 +7231,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H147" t="n">
         <v>0</v>
       </c>
-      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>ui_show_res:1005_Standard_SkeletonData&amp;ui_show_data:0.1312;0,0&amp;ui_show_skin:2</t>
@@ -7537,7 +7250,6 @@
           <t>星欲幻化药(StarLusts 1005/Standard/1005_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr">
         <is>
           <t>1</t>
@@ -7565,13 +7277,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H148" t="n">
         <v>0</v>
       </c>
-      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>ui_show_res:1005_Standard_SkeletonData&amp;ui_show_data:0.1312;0,0&amp;ui_show_skin:3</t>
@@ -7585,7 +7296,6 @@
           <t>星欲幻化药(StarLusts 1005/Standard/1005_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr">
         <is>
           <t>1</t>
@@ -7613,13 +7323,12 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H149" t="n">
         <v>0</v>
       </c>
-      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>ui_show_res:1006_CG_SkeletonData&amp;ui_show_data:0.208;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -7633,7 +7342,6 @@
           <t>星欲幻化药(StarLusts 1006/CG/1006_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr">
         <is>
           <t>1</t>
@@ -7661,13 +7369,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H150" t="n">
         <v>0</v>
       </c>
-      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>ui_show_res:1006_Standard_SkeletonData&amp;ui_show_data:0.1366;0,0&amp;ui_show_skin:1</t>
@@ -7681,7 +7388,6 @@
           <t>星欲幻化药(StarLusts 1006/Standard/1006_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr">
         <is>
           <t>1</t>
@@ -7709,13 +7415,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H151" t="n">
         <v>0</v>
       </c>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>ui_show_res:1006_Standard_SkeletonData&amp;ui_show_data:0.1366;0,0&amp;ui_show_skin:2</t>
@@ -7729,7 +7434,6 @@
           <t>星欲幻化药(StarLusts 1006/Standard/1006_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr">
         <is>
           <t>1</t>
@@ -7757,13 +7461,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H152" t="n">
         <v>0</v>
       </c>
-      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>ui_show_res:1006_Standard_SkeletonData&amp;ui_show_data:0.1366;0,0&amp;ui_show_skin:3</t>
@@ -7777,7 +7480,6 @@
           <t>星欲幻化药(StarLusts 1006/Standard/1006_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
           <t>1</t>
@@ -7805,13 +7507,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H153" t="n">
         <v>0</v>
       </c>
-      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>ui_show_res:1007_CG_SkeletonData&amp;ui_show_data:0.1069;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -7825,7 +7526,6 @@
           <t>星欲幻化药(StarLusts 1007/CG/1007_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr">
         <is>
           <t>1</t>
@@ -7853,13 +7553,12 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H154" t="n">
         <v>0</v>
       </c>
-      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>ui_show_res:1007_Standard_SkeletonData&amp;ui_show_data:0.136;0,0&amp;ui_show_skin:1</t>
@@ -7873,7 +7572,6 @@
           <t>星欲幻化药(StarLusts 1007/Standard/1007_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr">
         <is>
           <t>1</t>
@@ -7901,13 +7599,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H155" t="n">
         <v>0</v>
       </c>
-      <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
           <t>ui_show_res:1007_Standard_SkeletonData&amp;ui_show_data:0.136;0,0&amp;ui_show_skin:2</t>
@@ -7921,7 +7618,6 @@
           <t>星欲幻化药(StarLusts 1007/Standard/1007_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr">
         <is>
           <t>1</t>
@@ -7949,13 +7645,12 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H156" t="n">
         <v>0</v>
       </c>
-      <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
           <t>ui_show_res:1007_Standard_SkeletonData&amp;ui_show_data:0.136;0,0&amp;ui_show_skin:3</t>
@@ -7969,7 +7664,6 @@
           <t>星欲幻化药(StarLusts 1007/Standard/1007_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr">
         <is>
           <t>1</t>
@@ -7997,13 +7691,12 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H157" t="n">
         <v>0</v>
       </c>
-      <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
           <t>ui_show_res:1008_Standard_SkeletonData&amp;ui_show_data:0.1573;0,0&amp;ui_show_skin:1</t>
@@ -8017,7 +7710,6 @@
           <t>星欲幻化药(StarLusts 1008/Standard/1008_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr">
         <is>
           <t>1</t>
@@ -8045,13 +7737,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H158" t="n">
         <v>0</v>
       </c>
-      <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
           <t>ui_show_res:1008_Standard_SkeletonData&amp;ui_show_data:0.1573;0,0&amp;ui_show_skin:2</t>
@@ -8065,7 +7756,6 @@
           <t>星欲幻化药(StarLusts 1008/Standard/1008_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr">
         <is>
           <t>1</t>
@@ -8093,13 +7783,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H159" t="n">
         <v>0</v>
       </c>
-      <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>ui_show_res:1008_Standard_SkeletonData&amp;ui_show_data:0.1573;0,0&amp;ui_show_skin:3</t>
@@ -8113,7 +7802,6 @@
           <t>星欲幻化药(StarLusts 1008/Standard/1008_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr">
         <is>
           <t>1</t>
@@ -8141,13 +7829,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H160" t="n">
         <v>0</v>
       </c>
-      <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
           <t>ui_show_res:1009_Standard_SkeletonData&amp;ui_show_data:0.1303;0,0&amp;ui_show_skin:1</t>
@@ -8161,7 +7848,6 @@
           <t>星欲幻化药(StarLusts 1009/Standard/1009_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr">
         <is>
           <t>1</t>
@@ -8189,13 +7875,12 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H161" t="n">
         <v>0</v>
       </c>
-      <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
           <t>ui_show_res:1009_Standard_SkeletonData&amp;ui_show_data:0.1303;0,0&amp;ui_show_skin:2</t>
@@ -8209,7 +7894,6 @@
           <t>星欲幻化药(StarLusts 1009/Standard/1009_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr">
         <is>
           <t>1</t>
@@ -8237,13 +7921,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H162" t="n">
         <v>0</v>
       </c>
-      <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
           <t>ui_show_res:1009_Standard_SkeletonData&amp;ui_show_data:0.1303;0,0&amp;ui_show_skin:3</t>
@@ -8257,7 +7940,6 @@
           <t>星欲幻化药(StarLusts 1009/Standard/1009_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr">
         <is>
           <t>1</t>
@@ -8285,13 +7967,12 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H163" t="n">
         <v>0</v>
       </c>
-      <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
           <t>ui_show_res:1010_Standard_SkeletonData&amp;ui_show_data:0.1078;0,0&amp;ui_show_skin:1</t>
@@ -8305,7 +7986,6 @@
           <t>星欲幻化药(StarLusts 1010/Standard/1010_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr">
         <is>
           <t>1</t>
@@ -8333,13 +8013,12 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H164" t="n">
         <v>0</v>
       </c>
-      <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
           <t>ui_show_res:1010_Standard_SkeletonData&amp;ui_show_data:0.1078;0,0&amp;ui_show_skin:2</t>
@@ -8353,7 +8032,6 @@
           <t>星欲幻化药(StarLusts 1010/Standard/1010_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr">
         <is>
           <t>1</t>
@@ -8381,13 +8059,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H165" t="n">
         <v>0</v>
       </c>
-      <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
           <t>ui_show_res:1010_Standard_SkeletonData&amp;ui_show_data:0.1078;0,0&amp;ui_show_skin:3</t>
@@ -8401,7 +8078,6 @@
           <t>星欲幻化药(StarLusts 1010/Standard/1010_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M165" t="inlineStr"/>
       <c r="N165" t="inlineStr">
         <is>
           <t>1</t>
@@ -8429,13 +8105,12 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H166" t="n">
         <v>0</v>
       </c>
-      <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
           <t>ui_show_res:1011_Standard_SkeletonData&amp;ui_show_data:0.1357;0,0&amp;ui_show_skin:1</t>
@@ -8449,7 +8124,6 @@
           <t>星欲幻化药(StarLusts 1011/Standard/1011_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr">
         <is>
           <t>1</t>
@@ -8477,13 +8151,12 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H167" t="n">
         <v>0</v>
       </c>
-      <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
           <t>ui_show_res:1011_Standard_SkeletonData&amp;ui_show_data:0.1357;0,0&amp;ui_show_skin:2</t>
@@ -8497,7 +8170,6 @@
           <t>星欲幻化药(StarLusts 1011/Standard/1011_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr">
         <is>
           <t>1</t>
@@ -8525,13 +8197,12 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H168" t="n">
         <v>0</v>
       </c>
-      <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
           <t>ui_show_res:1011_Standard_SkeletonData&amp;ui_show_data:0.1357;0,0&amp;ui_show_skin:3</t>
@@ -8545,7 +8216,6 @@
           <t>星欲幻化药(StarLusts 1011/Standard/1011_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr">
         <is>
           <t>1</t>
@@ -8573,13 +8243,12 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H169" t="n">
         <v>0</v>
       </c>
-      <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
           <t>ui_show_res:1012_CG_SkeletonData&amp;ui_show_data:0.1352;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -8593,7 +8262,6 @@
           <t>星欲幻化药(StarLusts 1012/CG/1012_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr">
         <is>
           <t>1</t>
@@ -8621,13 +8289,12 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H170" t="n">
         <v>0</v>
       </c>
-      <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
           <t>ui_show_res:1012_Standard_SkeletonData&amp;ui_show_data:0.1244;0,0&amp;ui_show_skin:1</t>
@@ -8641,7 +8308,6 @@
           <t>星欲幻化药(StarLusts 1012/Standard/1012_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr">
         <is>
           <t>1</t>
@@ -8669,13 +8335,12 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H171" t="n">
         <v>0</v>
       </c>
-      <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
           <t>ui_show_res:1012_Standard_SkeletonData&amp;ui_show_data:0.1244;0,0&amp;ui_show_skin:2</t>
@@ -8689,7 +8354,6 @@
           <t>星欲幻化药(StarLusts 1012/Standard/1012_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr">
         <is>
           <t>1</t>
@@ -8717,13 +8381,12 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H172" t="n">
         <v>0</v>
       </c>
-      <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
           <t>ui_show_res:1012_Standard_SkeletonData&amp;ui_show_data:0.1244;0,0&amp;ui_show_skin:3</t>
@@ -8737,7 +8400,6 @@
           <t>星欲幻化药(StarLusts 1012/Standard/1012_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr">
         <is>
           <t>1</t>
@@ -8765,13 +8427,12 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H173" t="n">
         <v>0</v>
       </c>
-      <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
           <t>ui_show_res:1013_Standard_SkeletonData&amp;ui_show_data:0.1131;0,0&amp;ui_show_skin:1</t>
@@ -8785,7 +8446,6 @@
           <t>星欲幻化药(StarLusts 1013/Standard/1013_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr">
         <is>
           <t>1</t>
@@ -8813,13 +8473,12 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H174" t="n">
         <v>0</v>
       </c>
-      <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
           <t>ui_show_res:1013_Standard_SkeletonData&amp;ui_show_data:0.1131;0,0&amp;ui_show_skin:2</t>
@@ -8833,7 +8492,6 @@
           <t>星欲幻化药(StarLusts 1013/Standard/1013_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr">
         <is>
           <t>1</t>
@@ -8861,13 +8519,12 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H175" t="n">
         <v>0</v>
       </c>
-      <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
           <t>ui_show_res:1013_Standard_SkeletonData&amp;ui_show_data:0.1131;0,0&amp;ui_show_skin:3</t>
@@ -8881,7 +8538,6 @@
           <t>星欲幻化药(StarLusts 1013/Standard/1013_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr">
         <is>
           <t>1</t>
@@ -8909,13 +8565,12 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H176" t="n">
         <v>0</v>
       </c>
-      <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
           <t>ui_show_res:1014_Standard_SkeletonData&amp;ui_show_data:0.105;0,0&amp;ui_show_skin:1</t>
@@ -8929,7 +8584,6 @@
           <t>星欲幻化药(StarLusts 1014/Standard/1014_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr">
         <is>
           <t>1</t>
@@ -8957,13 +8611,12 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H177" t="n">
         <v>0</v>
       </c>
-      <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
           <t>ui_show_res:1014_Standard_SkeletonData&amp;ui_show_data:0.105;0,0&amp;ui_show_skin:2</t>
@@ -8977,7 +8630,6 @@
           <t>星欲幻化药(StarLusts 1014/Standard/1014_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr">
         <is>
           <t>1</t>
@@ -9005,13 +8657,12 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H178" t="n">
         <v>0</v>
       </c>
-      <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
           <t>ui_show_res:1014_Standard_SkeletonData&amp;ui_show_data:0.105;0,0&amp;ui_show_skin:3</t>
@@ -9025,7 +8676,6 @@
           <t>星欲幻化药(StarLusts 1014/Standard/1014_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr">
         <is>
           <t>1</t>
@@ -9053,13 +8703,12 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H179" t="n">
         <v>0</v>
       </c>
-      <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
           <t>ui_show_res:1015_CG_SkeletonData&amp;ui_show_data:0.102;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -9073,7 +8722,6 @@
           <t>星欲幻化药(StarLusts 1015/CG/1015_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr">
         <is>
           <t>1</t>
@@ -9101,13 +8749,12 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H180" t="n">
         <v>0</v>
       </c>
-      <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
           <t>ui_show_res:1015_Standard_SkeletonData&amp;ui_show_data:0.1319;0,0&amp;ui_show_skin:1</t>
@@ -9121,7 +8768,6 @@
           <t>星欲幻化药(StarLusts 1015/Standard/1015_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M180" t="inlineStr"/>
       <c r="N180" t="inlineStr">
         <is>
           <t>1</t>
@@ -9149,13 +8795,12 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H181" t="n">
         <v>0</v>
       </c>
-      <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
           <t>ui_show_res:1015_Standard_SkeletonData&amp;ui_show_data:0.1319;0,0&amp;ui_show_skin:2</t>
@@ -9169,7 +8814,6 @@
           <t>星欲幻化药(StarLusts 1015/Standard/1015_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr">
         <is>
           <t>1</t>
@@ -9197,13 +8841,12 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H182" t="n">
         <v>0</v>
       </c>
-      <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
           <t>ui_show_res:1015_Standard_SkeletonData&amp;ui_show_data:0.1319;0,0&amp;ui_show_skin:3</t>
@@ -9217,7 +8860,6 @@
           <t>星欲幻化药(StarLusts 1015/Standard/1015_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr">
         <is>
           <t>1</t>
@@ -9245,13 +8887,12 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H183" t="n">
         <v>0</v>
       </c>
-      <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
           <t>ui_show_res:1016_CG_SkeletonData&amp;ui_show_data:0.0907;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -9265,7 +8906,6 @@
           <t>星欲幻化药(StarLusts 1016/CG/1016_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr">
         <is>
           <t>1</t>
@@ -9293,13 +8933,12 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H184" t="n">
         <v>0</v>
       </c>
-      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
           <t>ui_show_res:1016_Standard_SkeletonData&amp;ui_show_data:0.0961;0,0&amp;ui_show_skin:1</t>
@@ -9313,7 +8952,6 @@
           <t>星欲幻化药(StarLusts 1016/Standard/1016_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr">
         <is>
           <t>1</t>
@@ -9341,13 +8979,12 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H185" t="n">
         <v>0</v>
       </c>
-      <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
           <t>ui_show_res:1016_Standard_SkeletonData&amp;ui_show_data:0.0961;0,0&amp;ui_show_skin:2</t>
@@ -9361,7 +8998,6 @@
           <t>星欲幻化药(StarLusts 1016/Standard/1016_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr">
         <is>
           <t>1</t>
@@ -9389,13 +9025,12 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H186" t="n">
         <v>0</v>
       </c>
-      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
           <t>ui_show_res:1016_Standard_SkeletonData&amp;ui_show_data:0.0961;0,0&amp;ui_show_skin:3</t>
@@ -9409,7 +9044,6 @@
           <t>星欲幻化药(StarLusts 1016/Standard/1016_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr">
         <is>
           <t>1</t>
@@ -9437,13 +9071,12 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H187" t="n">
         <v>0</v>
       </c>
-      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
           <t>ui_show_res:1017_CG_SkeletonData&amp;ui_show_data:0.0982;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -9457,7 +9090,6 @@
           <t>星欲幻化药(StarLusts 1017/CG/1017_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr">
         <is>
           <t>1</t>
@@ -9485,13 +9117,12 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H188" t="n">
         <v>0</v>
       </c>
-      <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
           <t>ui_show_res:1017_Standard_SkeletonData&amp;ui_show_data:0.1163;0,0&amp;ui_show_skin:1</t>
@@ -9505,7 +9136,6 @@
           <t>星欲幻化药(StarLusts 1017/Standard/1017_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr">
         <is>
           <t>1</t>
@@ -9533,13 +9163,12 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H189" t="n">
         <v>0</v>
       </c>
-      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
           <t>ui_show_res:1017_Standard_SkeletonData&amp;ui_show_data:0.1163;0,0&amp;ui_show_skin:2</t>
@@ -9553,7 +9182,6 @@
           <t>星欲幻化药(StarLusts 1017/Standard/1017_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr">
         <is>
           <t>1</t>
@@ -9581,13 +9209,12 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H190" t="n">
         <v>0</v>
       </c>
-      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
           <t>ui_show_res:1017_Standard_SkeletonData&amp;ui_show_data:0.1163;0,0&amp;ui_show_skin:3</t>
@@ -9601,7 +9228,6 @@
           <t>星欲幻化药(StarLusts 1017/Standard/1017_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr">
         <is>
           <t>1</t>
@@ -9629,13 +9255,12 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H191" t="n">
         <v>0</v>
       </c>
-      <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
           <t>ui_show_res:1019_Standard_SkeletonData&amp;ui_show_data:0.1075;0,0&amp;ui_show_skin:1</t>
@@ -9649,7 +9274,6 @@
           <t>星欲幻化药(StarLusts 1019/Standard/1019_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr">
         <is>
           <t>1</t>
@@ -9677,13 +9301,12 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H192" t="n">
         <v>0</v>
       </c>
-      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
           <t>ui_show_res:1019_Standard_SkeletonData&amp;ui_show_data:0.1075;0,0&amp;ui_show_skin:2</t>
@@ -9697,7 +9320,6 @@
           <t>星欲幻化药(StarLusts 1019/Standard/1019_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr">
         <is>
           <t>1</t>
@@ -9725,13 +9347,12 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H193" t="n">
         <v>0</v>
       </c>
-      <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
           <t>ui_show_res:1019_Standard_SkeletonData&amp;ui_show_data:0.1075;0,0&amp;ui_show_skin:3</t>
@@ -9745,7 +9366,6 @@
           <t>星欲幻化药(StarLusts 1019/Standard/1019_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M193" t="inlineStr"/>
       <c r="N193" t="inlineStr">
         <is>
           <t>1</t>
@@ -9773,13 +9393,12 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H194" t="n">
         <v>0</v>
       </c>
-      <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
           <t>ui_show_res:1020_CG_SkeletonData&amp;ui_show_data:0.1289;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -9793,7 +9412,6 @@
           <t>星欲幻化药(StarLusts 1020/CG/1020_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr">
         <is>
           <t>1</t>
@@ -9821,13 +9439,12 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H195" t="n">
         <v>0</v>
       </c>
-      <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
           <t>ui_show_res:1020_Standard_SkeletonData&amp;ui_show_data:0.163;0,0&amp;ui_show_skin:1</t>
@@ -9841,7 +9458,6 @@
           <t>星欲幻化药(StarLusts 1020/Standard/1020_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr">
         <is>
           <t>1</t>
@@ -9869,13 +9485,12 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H196" t="n">
         <v>0</v>
       </c>
-      <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
           <t>ui_show_res:1020_Standard_SkeletonData&amp;ui_show_data:0.163;0,0&amp;ui_show_skin:2</t>
@@ -9889,7 +9504,6 @@
           <t>星欲幻化药(StarLusts 1020/Standard/1020_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr">
         <is>
           <t>1</t>
@@ -9917,13 +9531,12 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H197" t="n">
         <v>0</v>
       </c>
-      <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
           <t>ui_show_res:1020_Standard_SkeletonData&amp;ui_show_data:0.163;0,0&amp;ui_show_skin:3</t>
@@ -9937,7 +9550,6 @@
           <t>星欲幻化药(StarLusts 1020/Standard/1020_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr">
         <is>
           <t>1</t>
@@ -9965,13 +9577,12 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H198" t="n">
         <v>0</v>
       </c>
-      <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
           <t>ui_show_res:2001_Standard_SkeletonData&amp;ui_show_data:0.1063;0,0&amp;ui_show_skin:1</t>
@@ -9985,7 +9596,6 @@
           <t>星欲幻化药(StarLusts 2001/Standard/2001_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr">
         <is>
           <t>1</t>
@@ -10013,13 +9623,12 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H199" t="n">
         <v>0</v>
       </c>
-      <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
           <t>ui_show_res:2001_Standard_SkeletonData&amp;ui_show_data:0.1063;0,0&amp;ui_show_skin:2</t>
@@ -10033,7 +9642,6 @@
           <t>星欲幻化药(StarLusts 2001/Standard/2001_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M199" t="inlineStr"/>
       <c r="N199" t="inlineStr">
         <is>
           <t>1</t>
@@ -10061,13 +9669,12 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H200" t="n">
         <v>0</v>
       </c>
-      <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
           <t>ui_show_res:2001_Standard_SkeletonData&amp;ui_show_data:0.1063;0,0&amp;ui_show_skin:3</t>
@@ -10081,7 +9688,6 @@
           <t>星欲幻化药(StarLusts 2001/Standard/2001_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr">
         <is>
           <t>1</t>
@@ -10109,13 +9715,12 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H201" t="n">
         <v>0</v>
       </c>
-      <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
           <t>ui_show_res:2002_Standard_SkeletonData&amp;ui_show_data:0.1312;0,0&amp;ui_show_skin:1</t>
@@ -10129,7 +9734,6 @@
           <t>星欲幻化药(StarLusts 2002/Standard/2002_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr">
         <is>
           <t>1</t>
@@ -10157,13 +9761,12 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H202" t="n">
         <v>0</v>
       </c>
-      <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
           <t>ui_show_res:2002_Standard_SkeletonData&amp;ui_show_data:0.1312;0,0&amp;ui_show_skin:2</t>
@@ -10177,7 +9780,6 @@
           <t>星欲幻化药(StarLusts 2002/Standard/2002_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr">
         <is>
           <t>1</t>
@@ -10205,13 +9807,12 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H203" t="n">
         <v>0</v>
       </c>
-      <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
           <t>ui_show_res:2002_Standard_SkeletonData&amp;ui_show_data:0.1312;0,0&amp;ui_show_skin:3</t>
@@ -10225,7 +9826,6 @@
           <t>星欲幻化药(StarLusts 2002/Standard/2002_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr">
         <is>
           <t>1</t>
@@ -10253,13 +9853,12 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H204" t="n">
         <v>0</v>
       </c>
-      <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
           <t>ui_show_res:2003_CG_SkeletonData&amp;ui_show_data:0.2116;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -10273,7 +9872,6 @@
           <t>星欲幻化药(StarLusts 2003/CG/2003_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr">
         <is>
           <t>1</t>
@@ -10301,13 +9899,12 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H205" t="n">
         <v>0</v>
       </c>
-      <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
           <t>ui_show_res:2003_Standard_SkeletonData&amp;ui_show_data:0.1322;0,0&amp;ui_show_skin:1</t>
@@ -10321,7 +9918,6 @@
           <t>星欲幻化药(StarLusts 2003/Standard/2003_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr">
         <is>
           <t>1</t>
@@ -10349,13 +9945,12 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H206" t="n">
         <v>0</v>
       </c>
-      <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
           <t>ui_show_res:2003_Standard_SkeletonData&amp;ui_show_data:0.1322;0,0&amp;ui_show_skin:2</t>
@@ -10369,7 +9964,6 @@
           <t>星欲幻化药(StarLusts 2003/Standard/2003_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr">
         <is>
           <t>1</t>
@@ -10397,13 +9991,12 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H207" t="n">
         <v>0</v>
       </c>
-      <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
           <t>ui_show_res:2003_Standard_SkeletonData&amp;ui_show_data:0.1322;0,0&amp;ui_show_skin:3</t>
@@ -10417,7 +10010,6 @@
           <t>星欲幻化药(StarLusts 2003/Standard/2003_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr">
         <is>
           <t>1</t>
@@ -10445,13 +10037,12 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H208" t="n">
         <v>0</v>
       </c>
-      <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
           <t>ui_show_res:2004_Standard_SkeletonData&amp;ui_show_data:0.1441;0,0&amp;ui_show_skin:1</t>
@@ -10465,7 +10056,6 @@
           <t>星欲幻化药(StarLusts 2004/Standard/2004_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr">
         <is>
           <t>1</t>
@@ -10493,13 +10083,12 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H209" t="n">
         <v>0</v>
       </c>
-      <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
           <t>ui_show_res:2004_Standard_SkeletonData&amp;ui_show_data:0.1441;0,0&amp;ui_show_skin:2</t>
@@ -10513,7 +10102,6 @@
           <t>星欲幻化药(StarLusts 2004/Standard/2004_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M209" t="inlineStr"/>
       <c r="N209" t="inlineStr">
         <is>
           <t>1</t>
@@ -10541,13 +10129,12 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H210" t="n">
         <v>0</v>
       </c>
-      <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
           <t>ui_show_res:2004_Standard_SkeletonData&amp;ui_show_data:0.1441;0,0&amp;ui_show_skin:3</t>
@@ -10561,7 +10148,6 @@
           <t>星欲幻化药(StarLusts 2004/Standard/2004_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr">
         <is>
           <t>1</t>
@@ -10589,13 +10175,12 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H211" t="n">
         <v>0</v>
       </c>
-      <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>ui_show_res:2005_Standard_SkeletonData&amp;ui_show_data:0.1546;0,0&amp;ui_show_skin:1</t>
@@ -10609,7 +10194,6 @@
           <t>星欲幻化药(StarLusts 2005/Standard/2005_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M211" t="inlineStr"/>
       <c r="N211" t="inlineStr">
         <is>
           <t>1</t>
@@ -10637,13 +10221,12 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H212" t="n">
         <v>0</v>
       </c>
-      <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
           <t>ui_show_res:2005_Standard_SkeletonData&amp;ui_show_data:0.1546;0,0&amp;ui_show_skin:2</t>
@@ -10657,7 +10240,6 @@
           <t>星欲幻化药(StarLusts 2005/Standard/2005_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr">
         <is>
           <t>1</t>
@@ -10685,13 +10267,12 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H213" t="n">
         <v>0</v>
       </c>
-      <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
           <t>ui_show_res:2005_Standard_SkeletonData&amp;ui_show_data:0.1546;0,0&amp;ui_show_skin:3</t>
@@ -10705,7 +10286,6 @@
           <t>星欲幻化药(StarLusts 2005/Standard/2005_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M213" t="inlineStr"/>
       <c r="N213" t="inlineStr">
         <is>
           <t>1</t>
@@ -10733,13 +10313,12 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H214" t="n">
         <v>0</v>
       </c>
-      <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
           <t>ui_show_res:2006_Standard_SkeletonData&amp;ui_show_data:0.1389;0,0&amp;ui_show_skin:1</t>
@@ -10753,7 +10332,6 @@
           <t>星欲幻化药(StarLusts 2006/Standard/2006_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M214" t="inlineStr"/>
       <c r="N214" t="inlineStr">
         <is>
           <t>1</t>
@@ -10781,13 +10359,12 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H215" t="n">
         <v>0</v>
       </c>
-      <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
           <t>ui_show_res:2006_Standard_SkeletonData&amp;ui_show_data:0.1389;0,0&amp;ui_show_skin:2</t>
@@ -10801,7 +10378,6 @@
           <t>星欲幻化药(StarLusts 2006/Standard/2006_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M215" t="inlineStr"/>
       <c r="N215" t="inlineStr">
         <is>
           <t>1</t>
@@ -10829,13 +10405,12 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H216" t="n">
         <v>0</v>
       </c>
-      <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
           <t>ui_show_res:2006_Standard_SkeletonData&amp;ui_show_data:0.1389;0,0&amp;ui_show_skin:3</t>
@@ -10849,7 +10424,6 @@
           <t>星欲幻化药(StarLusts 2006/Standard/2006_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr">
         <is>
           <t>1</t>
@@ -10877,13 +10451,12 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H217" t="n">
         <v>0</v>
       </c>
-      <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
           <t>ui_show_res:2007_Standard_SkeletonData&amp;ui_show_data:0.1518;0,0&amp;ui_show_skin:1</t>
@@ -10897,7 +10470,6 @@
           <t>星欲幻化药(StarLusts 2007/Standard/2007_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr">
         <is>
           <t>1</t>
@@ -10925,13 +10497,12 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H218" t="n">
         <v>0</v>
       </c>
-      <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
           <t>ui_show_res:2007_Standard_SkeletonData&amp;ui_show_data:0.1518;0,0&amp;ui_show_skin:2</t>
@@ -10945,7 +10516,6 @@
           <t>星欲幻化药(StarLusts 2007/Standard/2007_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr">
         <is>
           <t>1</t>
@@ -10973,13 +10543,12 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H219" t="n">
         <v>0</v>
       </c>
-      <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
           <t>ui_show_res:2007_Standard_SkeletonData&amp;ui_show_data:0.1518;0,0&amp;ui_show_skin:3</t>
@@ -10993,7 +10562,6 @@
           <t>星欲幻化药(StarLusts 2007/Standard/2007_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr">
         <is>
           <t>1</t>
@@ -11021,13 +10589,12 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H220" t="n">
         <v>0</v>
       </c>
-      <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
           <t>ui_show_res:2008_Standard_SkeletonData&amp;ui_show_data:0.1269;0,0&amp;ui_show_skin:1</t>
@@ -11041,7 +10608,6 @@
           <t>星欲幻化药(StarLusts 2008/Standard/2008_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr">
         <is>
           <t>1</t>
@@ -11069,13 +10635,12 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H221" t="n">
         <v>0</v>
       </c>
-      <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
           <t>ui_show_res:2008_Standard_SkeletonData&amp;ui_show_data:0.1269;0,0&amp;ui_show_skin:2</t>
@@ -11089,7 +10654,6 @@
           <t>星欲幻化药(StarLusts 2008/Standard/2008_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr">
         <is>
           <t>1</t>
@@ -11117,13 +10681,12 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H222" t="n">
         <v>0</v>
       </c>
-      <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
           <t>ui_show_res:2008_Standard_SkeletonData&amp;ui_show_data:0.1269;0,0&amp;ui_show_skin:3</t>
@@ -11137,7 +10700,6 @@
           <t>星欲幻化药(StarLusts 2008/Standard/2008_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M222" t="inlineStr"/>
       <c r="N222" t="inlineStr">
         <is>
           <t>1</t>
@@ -11165,13 +10727,12 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H223" t="n">
         <v>0</v>
       </c>
-      <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
           <t>ui_show_res:2009_CG_SkeletonData&amp;ui_show_data:0.1071;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -11185,7 +10746,6 @@
           <t>星欲幻化药(StarLusts 2009/CG/2009_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M223" t="inlineStr"/>
       <c r="N223" t="inlineStr">
         <is>
           <t>1</t>
@@ -11213,13 +10773,12 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H224" t="n">
         <v>0</v>
       </c>
-      <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
           <t>ui_show_res:2009_Standard_SkeletonData&amp;ui_show_data:0.1264;0,0&amp;ui_show_skin:1</t>
@@ -11233,7 +10792,6 @@
           <t>星欲幻化药(StarLusts 2009/Standard/2009_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M224" t="inlineStr"/>
       <c r="N224" t="inlineStr">
         <is>
           <t>1</t>
@@ -11261,13 +10819,12 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H225" t="n">
         <v>0</v>
       </c>
-      <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
           <t>ui_show_res:2009_Standard_SkeletonData&amp;ui_show_data:0.1264;0,0&amp;ui_show_skin:2</t>
@@ -11281,7 +10838,6 @@
           <t>星欲幻化药(StarLusts 2009/Standard/2009_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M225" t="inlineStr"/>
       <c r="N225" t="inlineStr">
         <is>
           <t>1</t>
@@ -11309,13 +10865,12 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H226" t="n">
         <v>0</v>
       </c>
-      <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
           <t>ui_show_res:2009_Standard_SkeletonData&amp;ui_show_data:0.1264;0,0&amp;ui_show_skin:3</t>
@@ -11329,7 +10884,6 @@
           <t>星欲幻化药(StarLusts 2009/Standard/2009_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M226" t="inlineStr"/>
       <c r="N226" t="inlineStr">
         <is>
           <t>1</t>
@@ -11357,13 +10911,12 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H227" t="n">
         <v>0</v>
       </c>
-      <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
           <t>ui_show_res:2010_Standard_SkeletonData&amp;ui_show_data:0.1694;0,0&amp;ui_show_skin:1</t>
@@ -11377,7 +10930,6 @@
           <t>星欲幻化药(StarLusts 2010/Standard/2010_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M227" t="inlineStr"/>
       <c r="N227" t="inlineStr">
         <is>
           <t>1</t>
@@ -11405,13 +10957,12 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H228" t="n">
         <v>0</v>
       </c>
-      <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
           <t>ui_show_res:2010_Standard_SkeletonData&amp;ui_show_data:0.1694;0,0&amp;ui_show_skin:2</t>
@@ -11425,7 +10976,6 @@
           <t>星欲幻化药(StarLusts 2010/Standard/2010_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr">
         <is>
           <t>1</t>
@@ -11453,13 +11003,12 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H229" t="n">
         <v>0</v>
       </c>
-      <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
           <t>ui_show_res:2010_Standard_SkeletonData&amp;ui_show_data:0.1694;0,0&amp;ui_show_skin:3</t>
@@ -11473,7 +11022,6 @@
           <t>星欲幻化药(StarLusts 2010/Standard/2010_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr">
         <is>
           <t>1</t>
@@ -11501,13 +11049,12 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H230" t="n">
         <v>0</v>
       </c>
-      <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
           <t>ui_show_res:2011_Standard_SkeletonData&amp;ui_show_data:0.1329;0,0&amp;ui_show_skin:1</t>
@@ -11521,7 +11068,6 @@
           <t>星欲幻化药(StarLusts 2011/Standard/2011_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M230" t="inlineStr"/>
       <c r="N230" t="inlineStr">
         <is>
           <t>1</t>
@@ -11549,13 +11095,12 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H231" t="n">
         <v>0</v>
       </c>
-      <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
           <t>ui_show_res:2011_Standard_SkeletonData&amp;ui_show_data:0.1329;0,0&amp;ui_show_skin:2</t>
@@ -11569,7 +11114,6 @@
           <t>星欲幻化药(StarLusts 2011/Standard/2011_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M231" t="inlineStr"/>
       <c r="N231" t="inlineStr">
         <is>
           <t>1</t>
@@ -11597,13 +11141,12 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H232" t="n">
         <v>0</v>
       </c>
-      <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
           <t>ui_show_res:2011_Standard_SkeletonData&amp;ui_show_data:0.1329;0,0&amp;ui_show_skin:3</t>
@@ -11617,7 +11160,6 @@
           <t>星欲幻化药(StarLusts 2011/Standard/2011_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M232" t="inlineStr"/>
       <c r="N232" t="inlineStr">
         <is>
           <t>1</t>
@@ -11645,13 +11187,12 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H233" t="n">
         <v>0</v>
       </c>
-      <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
           <t>ui_show_res:2012_Standard_SkeletonData&amp;ui_show_data:0.1112;0,0&amp;ui_show_skin:1</t>
@@ -11665,7 +11206,6 @@
           <t>星欲幻化药(StarLusts 2012/Standard/2012_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M233" t="inlineStr"/>
       <c r="N233" t="inlineStr">
         <is>
           <t>1</t>
@@ -11693,13 +11233,12 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H234" t="n">
         <v>0</v>
       </c>
-      <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr">
         <is>
           <t>ui_show_res:2012_Standard_SkeletonData&amp;ui_show_data:0.1112;0,0&amp;ui_show_skin:2</t>
@@ -11713,7 +11252,6 @@
           <t>星欲幻化药(StarLusts 2012/Standard/2012_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M234" t="inlineStr"/>
       <c r="N234" t="inlineStr">
         <is>
           <t>1</t>
@@ -11741,13 +11279,12 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H235" t="n">
         <v>0</v>
       </c>
-      <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr">
         <is>
           <t>ui_show_res:2012_Standard_SkeletonData&amp;ui_show_data:0.1112;0,0&amp;ui_show_skin:3</t>
@@ -11761,7 +11298,6 @@
           <t>星欲幻化药(StarLusts 2012/Standard/2012_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M235" t="inlineStr"/>
       <c r="N235" t="inlineStr">
         <is>
           <t>1</t>
@@ -11789,13 +11325,12 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H236" t="n">
         <v>0</v>
       </c>
-      <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr">
         <is>
           <t>ui_show_res:2013_CG_SkeletonData&amp;ui_show_data:0.121;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -11809,7 +11344,6 @@
           <t>星欲幻化药(StarLusts 2013/CG/2013_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M236" t="inlineStr"/>
       <c r="N236" t="inlineStr">
         <is>
           <t>1</t>
@@ -11837,13 +11371,12 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H237" t="n">
         <v>0</v>
       </c>
-      <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr">
         <is>
           <t>ui_show_res:2013_Standard_SkeletonData&amp;ui_show_data:0.1269;0,0&amp;ui_show_skin:1</t>
@@ -11857,7 +11390,6 @@
           <t>星欲幻化药(StarLusts 2013/Standard/2013_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M237" t="inlineStr"/>
       <c r="N237" t="inlineStr">
         <is>
           <t>1</t>
@@ -11885,13 +11417,12 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H238" t="n">
         <v>0</v>
       </c>
-      <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
           <t>ui_show_res:2013_Standard_SkeletonData&amp;ui_show_data:0.1269;0,0&amp;ui_show_skin:2</t>
@@ -11905,7 +11436,6 @@
           <t>星欲幻化药(StarLusts 2013/Standard/2013_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M238" t="inlineStr"/>
       <c r="N238" t="inlineStr">
         <is>
           <t>1</t>
@@ -11933,13 +11463,12 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H239" t="n">
         <v>0</v>
       </c>
-      <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr">
         <is>
           <t>ui_show_res:2013_Standard_SkeletonData&amp;ui_show_data:0.1269;0,0&amp;ui_show_skin:3</t>
@@ -11953,7 +11482,6 @@
           <t>星欲幻化药(StarLusts 2013/Standard/2013_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M239" t="inlineStr"/>
       <c r="N239" t="inlineStr">
         <is>
           <t>1</t>
@@ -11981,13 +11509,12 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H240" t="n">
         <v>0</v>
       </c>
-      <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr">
         <is>
           <t>ui_show_res:2014_CG_SkeletonData&amp;ui_show_data:0.151;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -12001,7 +11528,6 @@
           <t>星欲幻化药(StarLusts 2014/CG/2014_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M240" t="inlineStr"/>
       <c r="N240" t="inlineStr">
         <is>
           <t>1</t>
@@ -12029,13 +11555,12 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H241" t="n">
         <v>0</v>
       </c>
-      <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr">
         <is>
           <t>ui_show_res:2014_Standard_SkeletonData&amp;ui_show_data:0.1294;0,0&amp;ui_show_skin:1</t>
@@ -12049,7 +11574,6 @@
           <t>星欲幻化药(StarLusts 2014/Standard/2014_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M241" t="inlineStr"/>
       <c r="N241" t="inlineStr">
         <is>
           <t>1</t>
@@ -12077,13 +11601,12 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H242" t="n">
         <v>0</v>
       </c>
-      <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
           <t>ui_show_res:2014_Standard_SkeletonData&amp;ui_show_data:0.1294;0,0&amp;ui_show_skin:2</t>
@@ -12097,7 +11620,6 @@
           <t>星欲幻化药(StarLusts 2014/Standard/2014_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M242" t="inlineStr"/>
       <c r="N242" t="inlineStr">
         <is>
           <t>1</t>
@@ -12125,13 +11647,12 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H243" t="n">
         <v>0</v>
       </c>
-      <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
           <t>ui_show_res:2014_Standard_SkeletonData&amp;ui_show_data:0.1294;0,0&amp;ui_show_skin:3</t>
@@ -12145,7 +11666,6 @@
           <t>星欲幻化药(StarLusts 2014/Standard/2014_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M243" t="inlineStr"/>
       <c r="N243" t="inlineStr">
         <is>
           <t>1</t>
@@ -12173,13 +11693,12 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H244" t="n">
         <v>0</v>
       </c>
-      <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr">
         <is>
           <t>ui_show_res:2016_CG_SkeletonData&amp;ui_show_data:0.1203;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -12193,7 +11712,6 @@
           <t>星欲幻化药(StarLusts 2016/CG/2016_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M244" t="inlineStr"/>
       <c r="N244" t="inlineStr">
         <is>
           <t>1</t>
@@ -12221,13 +11739,12 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H245" t="n">
         <v>0</v>
       </c>
-      <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
           <t>ui_show_res:2016_Standard_SkeletonData&amp;ui_show_data:0.0877;0,0&amp;ui_show_skin:1</t>
@@ -12241,7 +11758,6 @@
           <t>星欲幻化药(StarLusts 2016/Standard/2016_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M245" t="inlineStr"/>
       <c r="N245" t="inlineStr">
         <is>
           <t>1</t>
@@ -12269,13 +11785,12 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H246" t="n">
         <v>0</v>
       </c>
-      <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
           <t>ui_show_res:2016_Standard_SkeletonData&amp;ui_show_data:0.0877;0,0&amp;ui_show_skin:2</t>
@@ -12289,7 +11804,6 @@
           <t>星欲幻化药(StarLusts 2016/Standard/2016_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M246" t="inlineStr"/>
       <c r="N246" t="inlineStr">
         <is>
           <t>1</t>
@@ -12317,13 +11831,12 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H247" t="n">
         <v>0</v>
       </c>
-      <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr">
         <is>
           <t>ui_show_res:2016_Standard_SkeletonData&amp;ui_show_data:0.0877;0,0&amp;ui_show_skin:3</t>
@@ -12337,7 +11850,6 @@
           <t>星欲幻化药(StarLusts 2016/Standard/2016_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M247" t="inlineStr"/>
       <c r="N247" t="inlineStr">
         <is>
           <t>1</t>
@@ -12365,13 +11877,12 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H248" t="n">
         <v>0</v>
       </c>
-      <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr">
         <is>
           <t>ui_show_res:2017_CG_SkeletonData&amp;ui_show_data:0.1189;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -12385,7 +11896,6 @@
           <t>星欲幻化药(StarLusts 2017/CG/2017_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M248" t="inlineStr"/>
       <c r="N248" t="inlineStr">
         <is>
           <t>1</t>
@@ -12413,13 +11923,12 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H249" t="n">
         <v>0</v>
       </c>
-      <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr">
         <is>
           <t>ui_show_res:2017_Standard_SkeletonData&amp;ui_show_data:0.1474;0,0&amp;ui_show_skin:1</t>
@@ -12433,7 +11942,6 @@
           <t>星欲幻化药(StarLusts 2017/Standard/2017_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M249" t="inlineStr"/>
       <c r="N249" t="inlineStr">
         <is>
           <t>1</t>
@@ -12461,13 +11969,12 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H250" t="n">
         <v>0</v>
       </c>
-      <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr">
         <is>
           <t>ui_show_res:2017_Standard_SkeletonData&amp;ui_show_data:0.1474;0,0&amp;ui_show_skin:2</t>
@@ -12481,7 +11988,6 @@
           <t>星欲幻化药(StarLusts 2017/Standard/2017_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M250" t="inlineStr"/>
       <c r="N250" t="inlineStr">
         <is>
           <t>1</t>
@@ -12509,13 +12015,12 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H251" t="n">
         <v>0</v>
       </c>
-      <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr">
         <is>
           <t>ui_show_res:2017_Standard_SkeletonData&amp;ui_show_data:0.1474;0,0&amp;ui_show_skin:3</t>
@@ -12529,7 +12034,6 @@
           <t>星欲幻化药(StarLusts 2017/Standard/2017_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M251" t="inlineStr"/>
       <c r="N251" t="inlineStr">
         <is>
           <t>1</t>
@@ -12557,13 +12061,12 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H252" t="n">
         <v>0</v>
       </c>
-      <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr">
         <is>
           <t>ui_show_res:2019_CG_SkeletonData&amp;ui_show_data:0.1066;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -12577,7 +12080,6 @@
           <t>星欲幻化药(StarLusts 2019/CG/2019_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M252" t="inlineStr"/>
       <c r="N252" t="inlineStr">
         <is>
           <t>1</t>
@@ -12605,13 +12107,12 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H253" t="n">
         <v>0</v>
       </c>
-      <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr">
         <is>
           <t>ui_show_res:2019_Standard_SkeletonData&amp;ui_show_data:0.1375;0,0&amp;ui_show_skin:1</t>
@@ -12625,7 +12126,6 @@
           <t>星欲幻化药(StarLusts 2019/Standard/2019_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M253" t="inlineStr"/>
       <c r="N253" t="inlineStr">
         <is>
           <t>1</t>
@@ -12653,13 +12153,12 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H254" t="n">
         <v>0</v>
       </c>
-      <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr">
         <is>
           <t>ui_show_res:2019_Standard_SkeletonData&amp;ui_show_data:0.1375;0,0&amp;ui_show_skin:2</t>
@@ -12673,7 +12172,6 @@
           <t>星欲幻化药(StarLusts 2019/Standard/2019_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M254" t="inlineStr"/>
       <c r="N254" t="inlineStr">
         <is>
           <t>1</t>
@@ -12701,13 +12199,12 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H255" t="n">
         <v>0</v>
       </c>
-      <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr">
         <is>
           <t>ui_show_res:2019_Standard_SkeletonData&amp;ui_show_data:0.1375;0,0&amp;ui_show_skin:3</t>
@@ -12721,7 +12218,6 @@
           <t>星欲幻化药(StarLusts 2019/Standard/2019_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M255" t="inlineStr"/>
       <c r="N255" t="inlineStr">
         <is>
           <t>1</t>
@@ -12749,13 +12245,12 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H256" t="n">
         <v>0</v>
       </c>
-      <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr">
         <is>
           <t>ui_show_res:2020_CG_SkeletonData&amp;ui_show_data:0.1146;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -12769,7 +12264,6 @@
           <t>星欲幻化药(StarLusts 2020/CG/2020_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M256" t="inlineStr"/>
       <c r="N256" t="inlineStr">
         <is>
           <t>1</t>
@@ -12797,13 +12291,12 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H257" t="n">
         <v>0</v>
       </c>
-      <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr">
         <is>
           <t>ui_show_res:2020_Standard_SkeletonData&amp;ui_show_data:0.1474;0,0&amp;ui_show_skin:1</t>
@@ -12817,7 +12310,6 @@
           <t>星欲幻化药(StarLusts 2020/Standard/2020_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M257" t="inlineStr"/>
       <c r="N257" t="inlineStr">
         <is>
           <t>1</t>
@@ -12845,13 +12337,12 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H258" t="n">
         <v>0</v>
       </c>
-      <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr">
         <is>
           <t>ui_show_res:2020_Standard_SkeletonData&amp;ui_show_data:0.1474;0,0&amp;ui_show_skin:2</t>
@@ -12865,7 +12356,6 @@
           <t>星欲幻化药(StarLusts 2020/Standard/2020_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M258" t="inlineStr"/>
       <c r="N258" t="inlineStr">
         <is>
           <t>1</t>
@@ -12893,13 +12383,12 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H259" t="n">
         <v>0</v>
       </c>
-      <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr">
         <is>
           <t>ui_show_res:2020_Standard_SkeletonData&amp;ui_show_data:0.1474;0,0&amp;ui_show_skin:3</t>
@@ -12913,7 +12402,6 @@
           <t>星欲幻化药(StarLusts 2020/Standard/2020_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M259" t="inlineStr"/>
       <c r="N259" t="inlineStr">
         <is>
           <t>1</t>
@@ -12941,13 +12429,12 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H260" t="n">
         <v>0</v>
       </c>
-      <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr">
         <is>
           <t>ui_show_res:2301_CG_SkeletonData&amp;ui_show_data:0.1204;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -12961,7 +12448,6 @@
           <t>星欲幻化药(StarLusts 2301/CG/2301_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M260" t="inlineStr"/>
       <c r="N260" t="inlineStr">
         <is>
           <t>1</t>
@@ -12989,13 +12475,12 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H261" t="n">
         <v>0</v>
       </c>
-      <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr">
         <is>
           <t>ui_show_res:2501_CG_SkeletonData&amp;ui_show_data:0.1289;0,0&amp;ui_show_idle_anim:Interactive/P1_Idle</t>
@@ -13009,7 +12494,6 @@
           <t>星欲幻化药(StarLusts 2501/CG/2501_CG_SkeletonData.asset default皮 idle:Interactive/P1_Idle)</t>
         </is>
       </c>
-      <c r="M261" t="inlineStr"/>
       <c r="N261" t="inlineStr">
         <is>
           <t>1</t>
@@ -13037,13 +12521,12 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H262" t="n">
         <v>0</v>
       </c>
-      <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr">
         <is>
           <t>ui_show_res:2901_CG_SkeletonData&amp;ui_show_data:0.1289;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -13057,7 +12540,6 @@
           <t>星欲幻化药(StarLusts 2901/CG/2901_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M262" t="inlineStr"/>
       <c r="N262" t="inlineStr">
         <is>
           <t>1</t>
@@ -13085,13 +12567,12 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H263" t="n">
         <v>0</v>
       </c>
-      <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr">
         <is>
           <t>ui_show_res:3001_CG_SkeletonData&amp;ui_show_data:0.1109;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -13105,7 +12586,6 @@
           <t>星欲幻化药(StarLusts 3001/CG/3001_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M263" t="inlineStr"/>
       <c r="N263" t="inlineStr">
         <is>
           <t>1</t>
@@ -13133,13 +12613,12 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H264" t="n">
         <v>0</v>
       </c>
-      <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr">
         <is>
           <t>ui_show_res:3001_Standard_SkeletonData&amp;ui_show_data:0.1335;0,0&amp;ui_show_skin:1</t>
@@ -13153,7 +12632,6 @@
           <t>星欲幻化药(StarLusts 3001/Standard/3001_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M264" t="inlineStr"/>
       <c r="N264" t="inlineStr">
         <is>
           <t>1</t>
@@ -13181,13 +12659,12 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H265" t="n">
         <v>0</v>
       </c>
-      <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr">
         <is>
           <t>ui_show_res:3001_Standard_SkeletonData&amp;ui_show_data:0.1335;0,0&amp;ui_show_skin:2</t>
@@ -13201,7 +12678,6 @@
           <t>星欲幻化药(StarLusts 3001/Standard/3001_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M265" t="inlineStr"/>
       <c r="N265" t="inlineStr">
         <is>
           <t>1</t>
@@ -13229,13 +12705,12 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H266" t="n">
         <v>0</v>
       </c>
-      <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr">
         <is>
           <t>ui_show_res:3001_Standard_SkeletonData&amp;ui_show_data:0.1335;0,0&amp;ui_show_skin:3</t>
@@ -13249,7 +12724,6 @@
           <t>星欲幻化药(StarLusts 3001/Standard/3001_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M266" t="inlineStr"/>
       <c r="N266" t="inlineStr">
         <is>
           <t>1</t>
@@ -13277,13 +12751,12 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H267" t="n">
         <v>0</v>
       </c>
-      <c r="I267" t="inlineStr"/>
       <c r="J267" t="inlineStr">
         <is>
           <t>ui_show_res:3002_Standard_SkeletonData&amp;ui_show_data:0.1342;0,0&amp;ui_show_skin:1</t>
@@ -13297,7 +12770,6 @@
           <t>星欲幻化药(StarLusts 3002/Standard/3002_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M267" t="inlineStr"/>
       <c r="N267" t="inlineStr">
         <is>
           <t>1</t>
@@ -13325,13 +12797,12 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H268" t="n">
         <v>0</v>
       </c>
-      <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr">
         <is>
           <t>ui_show_res:3002_Standard_SkeletonData&amp;ui_show_data:0.1342;0,0&amp;ui_show_skin:2</t>
@@ -13345,7 +12816,6 @@
           <t>星欲幻化药(StarLusts 3002/Standard/3002_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M268" t="inlineStr"/>
       <c r="N268" t="inlineStr">
         <is>
           <t>1</t>
@@ -13373,13 +12843,12 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H269" t="n">
         <v>0</v>
       </c>
-      <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr">
         <is>
           <t>ui_show_res:3002_Standard_SkeletonData&amp;ui_show_data:0.1342;0,0&amp;ui_show_skin:3</t>
@@ -13393,7 +12862,6 @@
           <t>星欲幻化药(StarLusts 3002/Standard/3002_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M269" t="inlineStr"/>
       <c r="N269" t="inlineStr">
         <is>
           <t>1</t>
@@ -13421,13 +12889,12 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H270" t="n">
         <v>0</v>
       </c>
-      <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr">
         <is>
           <t>ui_show_res:3003_Standard_SkeletonData&amp;ui_show_data:0.1238;0,0&amp;ui_show_skin:1</t>
@@ -13441,7 +12908,6 @@
           <t>星欲幻化药(StarLusts 3003/Standard/3003_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M270" t="inlineStr"/>
       <c r="N270" t="inlineStr">
         <is>
           <t>1</t>
@@ -13469,13 +12935,12 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H271" t="n">
         <v>0</v>
       </c>
-      <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr">
         <is>
           <t>ui_show_res:3003_Standard_SkeletonData&amp;ui_show_data:0.1238;0,0&amp;ui_show_skin:2</t>
@@ -13489,7 +12954,6 @@
           <t>星欲幻化药(StarLusts 3003/Standard/3003_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M271" t="inlineStr"/>
       <c r="N271" t="inlineStr">
         <is>
           <t>1</t>
@@ -13517,13 +12981,12 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H272" t="n">
         <v>0</v>
       </c>
-      <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr">
         <is>
           <t>ui_show_res:3003_Standard_SkeletonData&amp;ui_show_data:0.1238;0,0&amp;ui_show_skin:3</t>
@@ -13537,7 +13000,6 @@
           <t>星欲幻化药(StarLusts 3003/Standard/3003_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M272" t="inlineStr"/>
       <c r="N272" t="inlineStr">
         <is>
           <t>1</t>
@@ -13565,13 +13027,12 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H273" t="n">
         <v>0</v>
       </c>
-      <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr">
         <is>
           <t>ui_show_res:3005_CG_SkeletonData&amp;ui_show_data:0.0871;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -13585,7 +13046,6 @@
           <t>星欲幻化药(StarLusts 3005/CG/3005_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M273" t="inlineStr"/>
       <c r="N273" t="inlineStr">
         <is>
           <t>1</t>
@@ -13613,13 +13073,12 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H274" t="n">
         <v>0</v>
       </c>
-      <c r="I274" t="inlineStr"/>
       <c r="J274" t="inlineStr">
         <is>
           <t>ui_show_res:3005_Standard_SkeletonData&amp;ui_show_data:0.1287;0,0&amp;ui_show_skin:1</t>
@@ -13633,7 +13092,6 @@
           <t>星欲幻化药(StarLusts 3005/Standard/3005_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M274" t="inlineStr"/>
       <c r="N274" t="inlineStr">
         <is>
           <t>1</t>
@@ -13661,13 +13119,12 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H275" t="n">
         <v>0</v>
       </c>
-      <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr">
         <is>
           <t>ui_show_res:3005_Standard_SkeletonData&amp;ui_show_data:0.1287;0,0&amp;ui_show_skin:2</t>
@@ -13681,7 +13138,6 @@
           <t>星欲幻化药(StarLusts 3005/Standard/3005_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M275" t="inlineStr"/>
       <c r="N275" t="inlineStr">
         <is>
           <t>1</t>
@@ -13709,13 +13165,12 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H276" t="n">
         <v>0</v>
       </c>
-      <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr">
         <is>
           <t>ui_show_res:3005_Standard_SkeletonData&amp;ui_show_data:0.1287;0,0&amp;ui_show_skin:3</t>
@@ -13729,7 +13184,6 @@
           <t>星欲幻化药(StarLusts 3005/Standard/3005_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M276" t="inlineStr"/>
       <c r="N276" t="inlineStr">
         <is>
           <t>1</t>
@@ -13757,13 +13211,12 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H277" t="n">
         <v>0</v>
       </c>
-      <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr">
         <is>
           <t>ui_show_res:3006_CG_SkeletonData&amp;ui_show_data:0.1244;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -13777,7 +13230,6 @@
           <t>星欲幻化药(StarLusts 3006/CG/3006_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M277" t="inlineStr"/>
       <c r="N277" t="inlineStr">
         <is>
           <t>1</t>
@@ -13805,13 +13257,12 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H278" t="n">
         <v>0</v>
       </c>
-      <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr">
         <is>
           <t>ui_show_res:3006_Standard_SkeletonData&amp;ui_show_data:0.1346;0,0&amp;ui_show_skin:1</t>
@@ -13825,7 +13276,6 @@
           <t>星欲幻化药(StarLusts 3006/Standard/3006_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M278" t="inlineStr"/>
       <c r="N278" t="inlineStr">
         <is>
           <t>1</t>
@@ -13853,13 +13303,12 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H279" t="n">
         <v>0</v>
       </c>
-      <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr">
         <is>
           <t>ui_show_res:3006_Standard_SkeletonData&amp;ui_show_data:0.1346;0,0&amp;ui_show_skin:2</t>
@@ -13873,7 +13322,6 @@
           <t>星欲幻化药(StarLusts 3006/Standard/3006_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M279" t="inlineStr"/>
       <c r="N279" t="inlineStr">
         <is>
           <t>1</t>
@@ -13901,13 +13349,12 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H280" t="n">
         <v>0</v>
       </c>
-      <c r="I280" t="inlineStr"/>
       <c r="J280" t="inlineStr">
         <is>
           <t>ui_show_res:3006_Standard_SkeletonData&amp;ui_show_data:0.1346;0,0&amp;ui_show_skin:3</t>
@@ -13921,7 +13368,6 @@
           <t>星欲幻化药(StarLusts 3006/Standard/3006_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M280" t="inlineStr"/>
       <c r="N280" t="inlineStr">
         <is>
           <t>1</t>
@@ -13949,13 +13395,12 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H281" t="n">
         <v>0</v>
       </c>
-      <c r="I281" t="inlineStr"/>
       <c r="J281" t="inlineStr">
         <is>
           <t>ui_show_res:3007_CG_SkeletonData&amp;ui_show_data:0.137;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -13969,7 +13414,6 @@
           <t>星欲幻化药(StarLusts 3007/CG/3007_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M281" t="inlineStr"/>
       <c r="N281" t="inlineStr">
         <is>
           <t>1</t>
@@ -13997,13 +13441,12 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H282" t="n">
         <v>0</v>
       </c>
-      <c r="I282" t="inlineStr"/>
       <c r="J282" t="inlineStr">
         <is>
           <t>ui_show_res:3007_Standard_SkeletonData&amp;ui_show_data:0.1283;0,0&amp;ui_show_skin:1</t>
@@ -14017,7 +13460,6 @@
           <t>星欲幻化药(StarLusts 3007/Standard/3007_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M282" t="inlineStr"/>
       <c r="N282" t="inlineStr">
         <is>
           <t>1</t>
@@ -14045,13 +13487,12 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H283" t="n">
         <v>0</v>
       </c>
-      <c r="I283" t="inlineStr"/>
       <c r="J283" t="inlineStr">
         <is>
           <t>ui_show_res:3007_Standard_SkeletonData&amp;ui_show_data:0.1283;0,0&amp;ui_show_skin:2</t>
@@ -14065,7 +13506,6 @@
           <t>星欲幻化药(StarLusts 3007/Standard/3007_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M283" t="inlineStr"/>
       <c r="N283" t="inlineStr">
         <is>
           <t>1</t>
@@ -14093,13 +13533,12 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H284" t="n">
         <v>0</v>
       </c>
-      <c r="I284" t="inlineStr"/>
       <c r="J284" t="inlineStr">
         <is>
           <t>ui_show_res:3007_Standard_SkeletonData&amp;ui_show_data:0.1283;0,0&amp;ui_show_skin:3</t>
@@ -14113,7 +13552,6 @@
           <t>星欲幻化药(StarLusts 3007/Standard/3007_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M284" t="inlineStr"/>
       <c r="N284" t="inlineStr">
         <is>
           <t>1</t>
@@ -14141,13 +13579,12 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H285" t="n">
         <v>0</v>
       </c>
-      <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr">
         <is>
           <t>ui_show_res:3010_CG_SkeletonData&amp;ui_show_data:0.1166;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -14161,7 +13598,6 @@
           <t>星欲幻化药(StarLusts 3010/CG/3010_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M285" t="inlineStr"/>
       <c r="N285" t="inlineStr">
         <is>
           <t>1</t>
@@ -14189,13 +13625,12 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H286" t="n">
         <v>0</v>
       </c>
-      <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr">
         <is>
           <t>ui_show_res:3010_Standard_SkeletonData&amp;ui_show_data:0.1187;0,0&amp;ui_show_skin:1</t>
@@ -14209,7 +13644,6 @@
           <t>星欲幻化药(StarLusts 3010/Standard/3010_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M286" t="inlineStr"/>
       <c r="N286" t="inlineStr">
         <is>
           <t>1</t>
@@ -14237,13 +13671,12 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H287" t="n">
         <v>0</v>
       </c>
-      <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr">
         <is>
           <t>ui_show_res:3010_Standard_SkeletonData&amp;ui_show_data:0.1187;0,0&amp;ui_show_skin:2</t>
@@ -14257,7 +13690,6 @@
           <t>星欲幻化药(StarLusts 3010/Standard/3010_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M287" t="inlineStr"/>
       <c r="N287" t="inlineStr">
         <is>
           <t>1</t>
@@ -14285,13 +13717,12 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H288" t="n">
         <v>0</v>
       </c>
-      <c r="I288" t="inlineStr"/>
       <c r="J288" t="inlineStr">
         <is>
           <t>ui_show_res:3010_Standard_SkeletonData&amp;ui_show_data:0.1187;0,0&amp;ui_show_skin:3</t>
@@ -14305,7 +13736,6 @@
           <t>星欲幻化药(StarLusts 3010/Standard/3010_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M288" t="inlineStr"/>
       <c r="N288" t="inlineStr">
         <is>
           <t>1</t>
@@ -14333,13 +13763,12 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H289" t="n">
         <v>0</v>
       </c>
-      <c r="I289" t="inlineStr"/>
       <c r="J289" t="inlineStr">
         <is>
           <t>ui_show_res:3011_CG_SkeletonData&amp;ui_show_data:0.1565;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -14353,7 +13782,6 @@
           <t>星欲幻化药(StarLusts 3011/CG/3011_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M289" t="inlineStr"/>
       <c r="N289" t="inlineStr">
         <is>
           <t>1</t>
@@ -14381,13 +13809,12 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H290" t="n">
         <v>0</v>
       </c>
-      <c r="I290" t="inlineStr"/>
       <c r="J290" t="inlineStr">
         <is>
           <t>ui_show_res:3011_Standard_SkeletonData&amp;ui_show_data:0.125;0,0&amp;ui_show_skin:1</t>
@@ -14401,7 +13828,6 @@
           <t>星欲幻化药(StarLusts 3011/Standard/3011_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M290" t="inlineStr"/>
       <c r="N290" t="inlineStr">
         <is>
           <t>1</t>
@@ -14429,13 +13855,12 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H291" t="n">
         <v>0</v>
       </c>
-      <c r="I291" t="inlineStr"/>
       <c r="J291" t="inlineStr">
         <is>
           <t>ui_show_res:3011_Standard_SkeletonData&amp;ui_show_data:0.125;0,0&amp;ui_show_skin:2</t>
@@ -14449,7 +13874,6 @@
           <t>星欲幻化药(StarLusts 3011/Standard/3011_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M291" t="inlineStr"/>
       <c r="N291" t="inlineStr">
         <is>
           <t>1</t>
@@ -14477,13 +13901,12 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H292" t="n">
         <v>0</v>
       </c>
-      <c r="I292" t="inlineStr"/>
       <c r="J292" t="inlineStr">
         <is>
           <t>ui_show_res:3011_Standard_SkeletonData&amp;ui_show_data:0.125;0,0&amp;ui_show_skin:3</t>
@@ -14497,7 +13920,6 @@
           <t>星欲幻化药(StarLusts 3011/Standard/3011_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M292" t="inlineStr"/>
       <c r="N292" t="inlineStr">
         <is>
           <t>1</t>
@@ -14525,13 +13947,12 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H293" t="n">
         <v>0</v>
       </c>
-      <c r="I293" t="inlineStr"/>
       <c r="J293" t="inlineStr">
         <is>
           <t>ui_show_res:3012_CG_SkeletonData&amp;ui_show_data:0.099;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -14545,7 +13966,6 @@
           <t>星欲幻化药(StarLusts 3012/CG/3012_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M293" t="inlineStr"/>
       <c r="N293" t="inlineStr">
         <is>
           <t>1</t>
@@ -14573,13 +13993,12 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H294" t="n">
         <v>0</v>
       </c>
-      <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr">
         <is>
           <t>ui_show_res:3012_Standard_SkeletonData&amp;ui_show_data:0.1183;0,0&amp;ui_show_skin:1</t>
@@ -14593,7 +14012,6 @@
           <t>星欲幻化药(StarLusts 3012/Standard/3012_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M294" t="inlineStr"/>
       <c r="N294" t="inlineStr">
         <is>
           <t>1</t>
@@ -14621,13 +14039,12 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H295" t="n">
         <v>0</v>
       </c>
-      <c r="I295" t="inlineStr"/>
       <c r="J295" t="inlineStr">
         <is>
           <t>ui_show_res:3012_Standard_SkeletonData&amp;ui_show_data:0.1183;0,0&amp;ui_show_skin:2</t>
@@ -14641,7 +14058,6 @@
           <t>星欲幻化药(StarLusts 3012/Standard/3012_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M295" t="inlineStr"/>
       <c r="N295" t="inlineStr">
         <is>
           <t>1</t>
@@ -14669,13 +14085,12 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H296" t="n">
         <v>0</v>
       </c>
-      <c r="I296" t="inlineStr"/>
       <c r="J296" t="inlineStr">
         <is>
           <t>ui_show_res:3012_Standard_SkeletonData&amp;ui_show_data:0.1183;0,0&amp;ui_show_skin:3</t>
@@ -14689,7 +14104,6 @@
           <t>星欲幻化药(StarLusts 3012/Standard/3012_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M296" t="inlineStr"/>
       <c r="N296" t="inlineStr">
         <is>
           <t>1</t>
@@ -14717,13 +14131,12 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H297" t="n">
         <v>0</v>
       </c>
-      <c r="I297" t="inlineStr"/>
       <c r="J297" t="inlineStr">
         <is>
           <t>ui_show_res:3013_CG_SkeletonData&amp;ui_show_data:0.1062;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -14737,7 +14150,6 @@
           <t>星欲幻化药(StarLusts 3013/CG/3013_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M297" t="inlineStr"/>
       <c r="N297" t="inlineStr">
         <is>
           <t>1</t>
@@ -14765,13 +14177,12 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H298" t="n">
         <v>0</v>
       </c>
-      <c r="I298" t="inlineStr"/>
       <c r="J298" t="inlineStr">
         <is>
           <t>ui_show_res:3013_Standard_SkeletonData&amp;ui_show_data:0.1718;0,0&amp;ui_show_skin:1</t>
@@ -14785,7 +14196,6 @@
           <t>星欲幻化药(StarLusts 3013/Standard/3013_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M298" t="inlineStr"/>
       <c r="N298" t="inlineStr">
         <is>
           <t>1</t>
@@ -14813,13 +14223,12 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H299" t="n">
         <v>0</v>
       </c>
-      <c r="I299" t="inlineStr"/>
       <c r="J299" t="inlineStr">
         <is>
           <t>ui_show_res:3013_Standard_SkeletonData&amp;ui_show_data:0.1718;0,0&amp;ui_show_skin:2</t>
@@ -14833,7 +14242,6 @@
           <t>星欲幻化药(StarLusts 3013/Standard/3013_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M299" t="inlineStr"/>
       <c r="N299" t="inlineStr">
         <is>
           <t>1</t>
@@ -14861,13 +14269,12 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H300" t="n">
         <v>0</v>
       </c>
-      <c r="I300" t="inlineStr"/>
       <c r="J300" t="inlineStr">
         <is>
           <t>ui_show_res:3013_Standard_SkeletonData&amp;ui_show_data:0.1718;0,0&amp;ui_show_skin:3</t>
@@ -14881,7 +14288,6 @@
           <t>星欲幻化药(StarLusts 3013/Standard/3013_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M300" t="inlineStr"/>
       <c r="N300" t="inlineStr">
         <is>
           <t>1</t>
@@ -14909,13 +14315,12 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H301" t="n">
         <v>0</v>
       </c>
-      <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr">
         <is>
           <t>ui_show_res:3016_CG_SkeletonData&amp;ui_show_data:0.0923;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -14929,7 +14334,6 @@
           <t>星欲幻化药(StarLusts 3016/CG/3016_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M301" t="inlineStr"/>
       <c r="N301" t="inlineStr">
         <is>
           <t>1</t>
@@ -14957,13 +14361,12 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H302" t="n">
         <v>0</v>
       </c>
-      <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr">
         <is>
           <t>ui_show_res:3016_Standard_SkeletonData&amp;ui_show_data:0.1362;0,0&amp;ui_show_skin:1</t>
@@ -14977,7 +14380,6 @@
           <t>星欲幻化药(StarLusts 3016/Standard/3016_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M302" t="inlineStr"/>
       <c r="N302" t="inlineStr">
         <is>
           <t>1</t>
@@ -15005,13 +14407,12 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H303" t="n">
         <v>0</v>
       </c>
-      <c r="I303" t="inlineStr"/>
       <c r="J303" t="inlineStr">
         <is>
           <t>ui_show_res:3016_Standard_SkeletonData&amp;ui_show_data:0.1362;0,0&amp;ui_show_skin:2</t>
@@ -15025,7 +14426,6 @@
           <t>星欲幻化药(StarLusts 3016/Standard/3016_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M303" t="inlineStr"/>
       <c r="N303" t="inlineStr">
         <is>
           <t>1</t>
@@ -15053,13 +14453,12 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H304" t="n">
         <v>0</v>
       </c>
-      <c r="I304" t="inlineStr"/>
       <c r="J304" t="inlineStr">
         <is>
           <t>ui_show_res:3016_Standard_SkeletonData&amp;ui_show_data:0.1362;0,0&amp;ui_show_skin:3</t>
@@ -15073,7 +14472,6 @@
           <t>星欲幻化药(StarLusts 3016/Standard/3016_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M304" t="inlineStr"/>
       <c r="N304" t="inlineStr">
         <is>
           <t>1</t>
@@ -15101,13 +14499,12 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H305" t="n">
         <v>0</v>
       </c>
-      <c r="I305" t="inlineStr"/>
       <c r="J305" t="inlineStr">
         <is>
           <t>ui_show_res:4001_CG_SkeletonData&amp;ui_show_data:0.1264;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -15121,7 +14518,6 @@
           <t>星欲幻化药(StarLusts 4001/CG/4001_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M305" t="inlineStr"/>
       <c r="N305" t="inlineStr">
         <is>
           <t>1</t>
@@ -15149,13 +14545,12 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H306" t="n">
         <v>0</v>
       </c>
-      <c r="I306" t="inlineStr"/>
       <c r="J306" t="inlineStr">
         <is>
           <t>ui_show_res:4001_Standard_SkeletonData&amp;ui_show_data:0.133;0,0&amp;ui_show_skin:1</t>
@@ -15169,7 +14564,6 @@
           <t>星欲幻化药(StarLusts 4001/Standard/4001_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M306" t="inlineStr"/>
       <c r="N306" t="inlineStr">
         <is>
           <t>1</t>
@@ -15197,13 +14591,12 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H307" t="n">
         <v>0</v>
       </c>
-      <c r="I307" t="inlineStr"/>
       <c r="J307" t="inlineStr">
         <is>
           <t>ui_show_res:4001_Standard_SkeletonData&amp;ui_show_data:0.133;0,0&amp;ui_show_skin:2</t>
@@ -15217,7 +14610,6 @@
           <t>星欲幻化药(StarLusts 4001/Standard/4001_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M307" t="inlineStr"/>
       <c r="N307" t="inlineStr">
         <is>
           <t>1</t>
@@ -15245,13 +14637,12 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H308" t="n">
         <v>0</v>
       </c>
-      <c r="I308" t="inlineStr"/>
       <c r="J308" t="inlineStr">
         <is>
           <t>ui_show_res:4001_Standard_SkeletonData&amp;ui_show_data:0.133;0,0&amp;ui_show_skin:3</t>
@@ -15265,7 +14656,6 @@
           <t>星欲幻化药(StarLusts 4001/Standard/4001_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M308" t="inlineStr"/>
       <c r="N308" t="inlineStr">
         <is>
           <t>1</t>
@@ -15293,13 +14683,12 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H309" t="n">
         <v>0</v>
       </c>
-      <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr">
         <is>
           <t>ui_show_res:4002_CG_SkeletonData&amp;ui_show_data:0.1143;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -15313,7 +14702,6 @@
           <t>星欲幻化药(StarLusts 4002/CG/4002_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M309" t="inlineStr"/>
       <c r="N309" t="inlineStr">
         <is>
           <t>1</t>
@@ -15341,13 +14729,12 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H310" t="n">
         <v>0</v>
       </c>
-      <c r="I310" t="inlineStr"/>
       <c r="J310" t="inlineStr">
         <is>
           <t>ui_show_res:4002_Standard_SkeletonData&amp;ui_show_data:0.135;0,0&amp;ui_show_skin:1</t>
@@ -15361,7 +14748,6 @@
           <t>星欲幻化药(StarLusts 4002/Standard/4002_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M310" t="inlineStr"/>
       <c r="N310" t="inlineStr">
         <is>
           <t>1</t>
@@ -15389,13 +14775,12 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H311" t="n">
         <v>0</v>
       </c>
-      <c r="I311" t="inlineStr"/>
       <c r="J311" t="inlineStr">
         <is>
           <t>ui_show_res:4002_Standard_SkeletonData&amp;ui_show_data:0.135;0,0&amp;ui_show_skin:2</t>
@@ -15409,7 +14794,6 @@
           <t>星欲幻化药(StarLusts 4002/Standard/4002_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M311" t="inlineStr"/>
       <c r="N311" t="inlineStr">
         <is>
           <t>1</t>
@@ -15437,13 +14821,12 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H312" t="n">
         <v>0</v>
       </c>
-      <c r="I312" t="inlineStr"/>
       <c r="J312" t="inlineStr">
         <is>
           <t>ui_show_res:4002_Standard_SkeletonData&amp;ui_show_data:0.135;0,0&amp;ui_show_skin:3</t>
@@ -15457,7 +14840,6 @@
           <t>星欲幻化药(StarLusts 4002/Standard/4002_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M312" t="inlineStr"/>
       <c r="N312" t="inlineStr">
         <is>
           <t>1</t>
@@ -15485,13 +14867,12 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H313" t="n">
         <v>0</v>
       </c>
-      <c r="I313" t="inlineStr"/>
       <c r="J313" t="inlineStr">
         <is>
           <t>ui_show_res:4003_Standard_SkeletonData&amp;ui_show_data:0.1486;0,0&amp;ui_show_skin:1</t>
@@ -15505,7 +14886,6 @@
           <t>星欲幻化药(StarLusts 4003/Standard/4003_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M313" t="inlineStr"/>
       <c r="N313" t="inlineStr">
         <is>
           <t>1</t>
@@ -15533,13 +14913,12 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H314" t="n">
         <v>0</v>
       </c>
-      <c r="I314" t="inlineStr"/>
       <c r="J314" t="inlineStr">
         <is>
           <t>ui_show_res:4003_Standard_SkeletonData&amp;ui_show_data:0.1486;0,0&amp;ui_show_skin:2</t>
@@ -15553,7 +14932,6 @@
           <t>星欲幻化药(StarLusts 4003/Standard/4003_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M314" t="inlineStr"/>
       <c r="N314" t="inlineStr">
         <is>
           <t>1</t>
@@ -15581,13 +14959,12 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H315" t="n">
         <v>0</v>
       </c>
-      <c r="I315" t="inlineStr"/>
       <c r="J315" t="inlineStr">
         <is>
           <t>ui_show_res:4003_Standard_SkeletonData&amp;ui_show_data:0.1486;0,0&amp;ui_show_skin:3</t>
@@ -15601,7 +14978,6 @@
           <t>星欲幻化药(StarLusts 4003/Standard/4003_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M315" t="inlineStr"/>
       <c r="N315" t="inlineStr">
         <is>
           <t>1</t>
@@ -15629,13 +15005,12 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H316" t="n">
         <v>0</v>
       </c>
-      <c r="I316" t="inlineStr"/>
       <c r="J316" t="inlineStr">
         <is>
           <t>ui_show_res:4005_CG_SkeletonData&amp;ui_show_data:0.1235;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -15649,7 +15024,6 @@
           <t>星欲幻化药(StarLusts 4005/CG/4005_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M316" t="inlineStr"/>
       <c r="N316" t="inlineStr">
         <is>
           <t>1</t>
@@ -15677,13 +15051,12 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H317" t="n">
         <v>0</v>
       </c>
-      <c r="I317" t="inlineStr"/>
       <c r="J317" t="inlineStr">
         <is>
           <t>ui_show_res:4005_Standard_SkeletonData&amp;ui_show_data:0.1312;0,0&amp;ui_show_skin:1</t>
@@ -15697,7 +15070,6 @@
           <t>星欲幻化药(StarLusts 4005/Standard/4005_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M317" t="inlineStr"/>
       <c r="N317" t="inlineStr">
         <is>
           <t>1</t>
@@ -15725,13 +15097,12 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H318" t="n">
         <v>0</v>
       </c>
-      <c r="I318" t="inlineStr"/>
       <c r="J318" t="inlineStr">
         <is>
           <t>ui_show_res:4005_Standard_SkeletonData&amp;ui_show_data:0.1312;0,0&amp;ui_show_skin:2</t>
@@ -15745,7 +15116,6 @@
           <t>星欲幻化药(StarLusts 4005/Standard/4005_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M318" t="inlineStr"/>
       <c r="N318" t="inlineStr">
         <is>
           <t>1</t>
@@ -15773,13 +15143,12 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H319" t="n">
         <v>0</v>
       </c>
-      <c r="I319" t="inlineStr"/>
       <c r="J319" t="inlineStr">
         <is>
           <t>ui_show_res:4005_Standard_SkeletonData&amp;ui_show_data:0.1312;0,0&amp;ui_show_skin:3</t>
@@ -15793,7 +15162,6 @@
           <t>星欲幻化药(StarLusts 4005/Standard/4005_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M319" t="inlineStr"/>
       <c r="N319" t="inlineStr">
         <is>
           <t>1</t>
@@ -15821,13 +15189,12 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H320" t="n">
         <v>0</v>
       </c>
-      <c r="I320" t="inlineStr"/>
       <c r="J320" t="inlineStr">
         <is>
           <t>ui_show_res:4013_CG_SkeletonData&amp;ui_show_data:0.1075;0,0&amp;ui_show_idle_anim:InteractiveMode/P1_Idle</t>
@@ -15841,7 +15208,6 @@
           <t>星欲幻化药(StarLusts 4013/CG/4013_CG_SkeletonData.asset default皮 idle:InteractiveMode/P1_Idle)</t>
         </is>
       </c>
-      <c r="M320" t="inlineStr"/>
       <c r="N320" t="inlineStr">
         <is>
           <t>1</t>
@@ -15869,13 +15235,12 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H321" t="n">
         <v>0</v>
       </c>
-      <c r="I321" t="inlineStr"/>
       <c r="J321" t="inlineStr">
         <is>
           <t>ui_show_res:4013_Standard_SkeletonData&amp;ui_show_data:0.1305;0,0&amp;ui_show_skin:1</t>
@@ -15889,7 +15254,6 @@
           <t>星欲幻化药(StarLusts 4013/Standard/4013_Standard_SkeletonData.asset skin:1)</t>
         </is>
       </c>
-      <c r="M321" t="inlineStr"/>
       <c r="N321" t="inlineStr">
         <is>
           <t>1</t>
@@ -15917,13 +15281,12 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H322" t="n">
         <v>0</v>
       </c>
-      <c r="I322" t="inlineStr"/>
       <c r="J322" t="inlineStr">
         <is>
           <t>ui_show_res:4013_Standard_SkeletonData&amp;ui_show_data:0.1305;0,0&amp;ui_show_skin:2</t>
@@ -15937,7 +15300,6 @@
           <t>星欲幻化药(StarLusts 4013/Standard/4013_Standard_SkeletonData.asset skin:2)</t>
         </is>
       </c>
-      <c r="M322" t="inlineStr"/>
       <c r="N322" t="inlineStr">
         <is>
           <t>1</t>
@@ -15965,13 +15327,12 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H323" t="n">
         <v>0</v>
       </c>
-      <c r="I323" t="inlineStr"/>
       <c r="J323" t="inlineStr">
         <is>
           <t>ui_show_res:4013_Standard_SkeletonData&amp;ui_show_data:0.1305;0,0&amp;ui_show_skin:3</t>
@@ -15985,7 +15346,6 @@
           <t>星欲幻化药(StarLusts 4013/Standard/4013_Standard_SkeletonData.asset skin:3)</t>
         </is>
       </c>
-      <c r="M323" t="inlineStr"/>
       <c r="N323" t="inlineStr">
         <is>
           <t>1</t>
